--- a/data/original/freework02.xlsx
+++ b/data/original/freework02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="202508011232000170" r:id="rId3" sheetId="1"/>
+    <sheet name="202509051204000480" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -90,7 +90,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T67"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.0" customWidth="true"/>
@@ -99,7 +99,7 @@
     <col min="4" max="4" width="17.0" customWidth="true"/>
     <col min="5" max="5" width="17.0" customWidth="true"/>
     <col min="6" max="6" width="9.0" customWidth="true"/>
-    <col min="7" max="7" width="128.0" customWidth="true"/>
+    <col min="7" max="7" width="223.0" customWidth="true"/>
     <col min="8" max="8" width="94.0" customWidth="true"/>
     <col min="9" max="9" width="21.0" customWidth="true"/>
     <col min="10" max="10" width="19.0" customWidth="true"/>
@@ -108,11 +108,11 @@
     <col min="13" max="13" width="12.0" customWidth="true"/>
     <col min="14" max="14" width="12.0" customWidth="true"/>
     <col min="15" max="15" width="19.0" customWidth="true"/>
-    <col min="16" max="16" width="18.0" customWidth="true"/>
+    <col min="16" max="16" width="28.0" customWidth="true"/>
     <col min="17" max="17" width="39.0" customWidth="true"/>
-    <col min="18" max="18" width="29.0" customWidth="true"/>
+    <col min="18" max="18" width="26.0" customWidth="true"/>
     <col min="19" max="19" width="19.0" customWidth="true"/>
-    <col min="20" max="20" width="124.0" customWidth="true"/>
+    <col min="20" max="20" width="71.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -225,7 +225,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rXg0kz9CTQWdvWYf8fONSQ06491754022736</t>
+          <t>Ss_IUrU4SKSgI8XHy6ZqvQ06491757045088</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -235,12 +235,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-01 下午</t>
+          <t>2025-09-05 下午</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-08-01 下午</t>
+          <t>2025-09-05 下午</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -250,7 +250,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>家里有事</t>
+          <t>有事</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -260,37 +260,33 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>202508011232000165065</t>
+          <t>202509051204000481669</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-08-01 12:32:17</t>
+          <t>2025-09-05 12:04:48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>朱强</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>钟洪伟</t>
-        </is>
-      </c>
+          <t>秦国超</t>
+        </is>
+      </c>
+      <c r="L2"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-08-01 12:32:17</t>
+          <t>2025-09-05 13:30:51</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -300,22 +296,25 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>朱强提交的请假</t>
+          <t>秦国超提交的请假</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3:14:18</t>
+          <t>1:26:3</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>朱强|提交申请|2025-08-01 12:32:16|提交申请</t>
+          <t>秦国超|提交申请|2025-09-05 12:04:48|提交申请;
+钟洪伟|审批人|2025-09-05 12:15:14|同意|;
+董磊|直接主管|2025-09-05 13:30:51|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-05 13:30:51|抄送</t>
         </is>
       </c>
     </row>
@@ -327,32 +326,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>m1C127O0QKOVDm_tEiB19g06491753952574</t>
+          <t>NZUSQZOATbCAFhgjGpKu_A06491757030304</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-19 08:30</t>
+          <t>2025-09-05 上午</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-07-19 17:30</t>
+          <t>2025-09-05 下午</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>车间休息</t>
+          <t>去医院看一下脸</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -362,17 +361,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>202507311702000546750</t>
+          <t>202509050758000249476</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-07-31 17:02:54</t>
+          <t>2025-09-05 07:58:24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>马崇坤</t>
         </is>
       </c>
       <c r="L3"/>
@@ -388,36 +387,35 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-07-31 18:44:00</t>
+          <t>2025-09-05 16:48:32</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>杭州劳务</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>马崇坤提交的请假</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>段少波,张成林,李锋</t>
+          <t>董磊,钟洪伟</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1:41:7</t>
+          <t>8:50:9</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-31 17:02:54|提交申请;
-段少波|审批人|2025-07-31 17:06:34|同意|同意|;
-张成林|直接主管|2025-07-31 17:06:59|同意|;
-李锋|直接主管|2025-07-31 18:44:00|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-31 18:44:01|抄送</t>
+          <t>马崇坤|提交申请|2025-09-05 07:58:24|提交申请;
+钟洪伟|审批人|2025-09-05 10:16:16|同意|;
+董磊|审批人|2025-09-05 16:48:32|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-05 16:48:32|抄送</t>
         </is>
       </c>
     </row>
@@ -429,7 +427,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>oHhMMvqQSwm0XPI4qZlc8w06491753929078</t>
+          <t>gNOMhQymSdCyQQYItxUA9Q06491756955554</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -439,22 +437,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-07-31 13:30</t>
+          <t>2025-09-04 16:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-07-31 18:00</t>
+          <t>2025-09-04 18:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5小时</t>
+          <t>2小时</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>有事需请假半天</t>
+          <t>家里临时有事</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -464,61 +462,59 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>202507311031000189643</t>
+          <t>202509041112000347321</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2025-07-31 10:31:19</t>
+          <t>2025-09-04 11:12:34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>黄海波</t>
+          <t>周承成</t>
         </is>
       </c>
       <c r="L4"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-07-31 14:14:14</t>
+          <t>2025-09-04 11:12:34</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>系统开发部</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>黄海波提交的请假</t>
+          <t>周承成提交的请假</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>董磊,钟洪伟</t>
+          <t/>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3:42:56</t>
+          <t>0:25:24</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>黄海波|提交申请|2025-07-31 10:31:19|提交申请;
-钟洪伟|审批人|2025-07-31 13:19:13|同意|;
-董磊|直接主管|2025-07-31 14:14:14|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-31 14:14:14|抄送</t>
+          <t>周承成|提交申请|2025-09-04 11:12:34|提交申请;
+周承成|2025-09-04 11:37:58|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -530,32 +526,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QCc-7UyaTUaJBxMi-ZewZw06491753866858</t>
+          <t>t6q0PITZTLKrlyGsBgIvZg06491756949146</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-07-31 08:25</t>
+          <t>2025-09-04 下午</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-07-31 17:35</t>
+          <t>2025-09-04 下午</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>累计加班调休</t>
+          <t>有事</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -565,62 +561,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>202507301714000181215</t>
+          <t>202509040925000466156</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2025-07-30 17:14:18</t>
+          <t>2025-09-04 09:25:46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>马鸣强</t>
-        </is>
-      </c>
-      <c r="L5"/>
+          <t>陆尖</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>黄风丽</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-07-31 08:33:40</t>
+          <t>2025-09-04 09:25:46</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>马鸣强提交的请假</t>
+          <t>陆尖提交的请假</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t/>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15:19:23</t>
+          <t>32:48:34</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>马鸣强|提交申请|2025-07-30 17:14:18|提交申请;
-李锋|审批人|2025-07-30 18:23:57|同意|同意|;
-张成林|直接主管|2025-07-31 00:26:10|同意|;
-李锋|直接主管|2025-07-31 08:33:40|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-31 08:33:40|抄送</t>
+          <t>陆尖|提交申请|2025-09-04 09:25:46|提交申请</t>
         </is>
       </c>
     </row>
@@ -632,52 +628,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tKX3D6WVQdOcibVuu1Zo5A06491753841001</t>
+          <t>JXn35KjORCmJeczGc7D2QA06491756884114</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-07-26 08:30</t>
+          <t>2025-09-03 下午</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-07-26 17:30</t>
+          <t>2025-09-04 下午</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>1.5天</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>身体不适</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t/>
+          <t>https://static.dingtalk.com/media/lQDPM5E-moMGYBHND8DNC9Cwp7lIQoOnfr8IlTtB7FTkAA_3024_4032.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>202507301003000219930</t>
+          <t>202509031521000546988</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2025-07-30 10:03:21</t>
+          <t>2025-09-03 15:21:54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>朱强</t>
         </is>
       </c>
       <c r="L6"/>
@@ -693,36 +689,35 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2025-07-30 15:25:10</t>
+          <t>2025-09-05 16:47:42</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>朱强提交的请假</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>张成林,李锋,段少波</t>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>5:21:50</t>
+          <t>49:25:49</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 10:03:21|提交申请;
-段少波|审批人|2025-07-30 10:05:34|同意|同意|;
-张成林|直接主管|2025-07-30 13:58:19|同意|;
-李锋|直接主管|2025-07-30 15:25:10|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:25:10|抄送</t>
+          <t>朱强|提交申请|2025-09-03 15:21:54|提交申请;
+钟洪伟|审批人|2025-09-05 10:16:48|同意|;
+董磊|直接主管|2025-09-05 16:47:42|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-05 16:47:42|抄送</t>
         </is>
       </c>
     </row>
@@ -734,32 +729,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>h9twOr8uQDehKaruzL-x7w06491753840699</t>
+          <t>rmTCYAl1T3-DMx6txpEvag06491756877858</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-07-28 15:30</t>
+          <t>2025-09-03 下午</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-07-28 17:30</t>
+          <t>2025-09-03 下午</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>身体不适</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -769,62 +764,59 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>202507300958000190998</t>
+          <t>202509031337000386836</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2025-07-30 09:58:19</t>
+          <t>2025-09-03 13:37:38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>朱强</t>
         </is>
       </c>
       <c r="L7"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-07-30 15:26:21</t>
+          <t>2025-09-03 13:37:38</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>朱强提交的请假</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>段少波,张成林,李锋</t>
+          <t/>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>5:28:2</t>
+          <t>1:42:14</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:58:19|提交申请;
-段少波|审批人|2025-07-30 10:05:42|同意|同意|;
-张成林|直接主管|2025-07-30 13:58:12|同意|;
-李锋|直接主管|2025-07-30 15:26:21|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:26:21|抄送</t>
+          <t>朱强|提交申请|2025-09-03 13:37:38|提交申请;
+朱强|2025-09-03 15:19:51|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -836,7 +828,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6R3tYNs3TaipUl61TTChfw06491753840587</t>
+          <t>gHGwFwB3TeOXEnFCp_i3eg06491756720549</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -846,22 +838,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-07-18 13:00</t>
+          <t>2025-09-01 08:30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-07-18 17:30</t>
+          <t>2025-09-01 17:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.5小时</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -871,17 +863,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>202507300956000278067</t>
+          <t>202509011755000508260</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2025-07-30 09:56:27</t>
+          <t>2025-09-01 17:55:50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L8"/>
@@ -897,36 +889,35 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-07-30 15:26:10</t>
+          <t>2025-09-01 18:45:13</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>段少波,张成林,李锋</t>
+          <t>杜鸣,张健宁</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5:29:43</t>
+          <t>0:49:24</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:56:27|提交申请;
-段少波|审批人|2025-07-30 10:05:50|同意|同意|;
-张成林|直接主管|2025-07-30 13:58:04|同意|;
-李锋|直接主管|2025-07-30 15:26:10|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:26:10|抄送</t>
+          <t>王兴磊|提交申请|2025-09-01 17:55:50|提交申请;
+张健宁|审批人|2025-09-01 18:28:39|同意|;
+杜鸣|直接主管|2025-09-01 18:45:13|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-01 18:45:13|抄送</t>
         </is>
       </c>
     </row>
@@ -938,97 +929,99 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5LmjR3u-QDyq09F-fFixkA06491753840465</t>
+          <t>cc794zQtRVi0Av6OSBQKOA06491756713738</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>陪产假</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-17 15:00</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-07-17 17:30</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>12天</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>因妻子分娩，故请陪产假陪护，望领导批准！</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t/>
+          <t>https://static.dingtalk.com/media/lQDPD4TmdYvk1ZnNBQDNA8Cw3MHSTWjmodcIkrFHEycsAA_960_1280.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>202507300954000259134</t>
+          <t>202509011602000188230</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2025-07-30 09:54:25</t>
+          <t>2025-09-01 16:02:18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>陈登科</t>
-        </is>
-      </c>
-      <c r="L9"/>
+          <t>李运动</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>李萍</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-07-30 15:25:59</t>
+          <t>2025-09-05 17:08:26</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>李运动提交的请假</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>张成林,李锋,段少波</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>5:31:35</t>
+          <t>98:12:3</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:54:25|提交申请;
-段少波|审批人|2025-07-30 10:06:03|同意|同意|;
-张成林|直接主管|2025-07-30 13:57:58|同意|;
-李锋|直接主管|2025-07-30 15:25:59|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:25:59|抄送</t>
+          <t>李运动|提交申请|2025-09-01 16:02:18|提交申请;
+张健宁|审批人|2025-09-04 08:41:15|同意|;
+杜鸣|直接主管|2025-09-05 17:08:26|同意|</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1033,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZMZCFZXqTtmsolHJ8Z7WWQ06491753840417</t>
+          <t>p3US646kQkygOVqsqwiagw06491756548298</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1050,17 +1043,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07-15 15:00</t>
+          <t>2025-08-28 08:30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-07-15 17:30</t>
+          <t>2025-08-28 12:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>3.5小时</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1075,17 +1068,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>202507300953000372922</t>
+          <t>202508301804000586688</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-07-30 09:53:37</t>
+          <t>2025-08-30 18:04:58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L10"/>
@@ -1101,7 +1094,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-07-30 15:25:47</t>
+          <t>2025-09-01 08:27:15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1111,26 +1104,26 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>陈雄提交的请假</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>段少波,张成林,李锋</t>
+          <t>张成林,李锋,段少波</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>5:32:11</t>
+          <t>38:22:18</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:53:37|提交申请;
-段少波|审批人|2025-07-30 10:06:11|同意|同意|;
-张成林|直接主管|2025-07-30 13:57:51|同意|;
-李锋|直接主管|2025-07-30 15:25:47|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:25:48|抄送</t>
+          <t>陈雄|提交申请|2025-08-30 18:04:58|提交申请;
+段少波|审批人|2025-08-31 13:47:47|同意|同意|;
+张成林|直接主管|2025-08-31 13:48:02|同意|;
+李锋|直接主管|2025-09-01 08:27:15|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-01 08:27:15|抄送</t>
         </is>
       </c>
     </row>
@@ -1142,97 +1135,94 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4O80soBjTHC095wQ8eqXRA06491753840364</t>
+          <t>1M2hM3gQTVy9r0dCjOtIdg06491756442910</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-07-14 15:00</t>
+          <t>2025-08-30 上午</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-07-14 17:30</t>
+          <t>2025-09-05 下午</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>5天</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>心情不好去爬山</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t/>
+          <t>https://static.dingtalk.com/media/lQDPM5u5nOL1XzHNBQDNAtCwl_rnGDk3dZgIjqgrqdXOAA_720_1280.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>202507300952000446480</t>
+          <t>202508291248000306063</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-07-30 09:52:44</t>
+          <t>2025-08-29 12:48:30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>徐正亮</t>
         </is>
       </c>
       <c r="L11"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-07-30 15:25:37</t>
+          <t>2025-08-29 12:48:30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>杭州劳务</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>徐正亮提交的请假</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>张成林,李锋,段少波</t>
+          <t/>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>5:32:52</t>
+          <t>5:37:6</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:52:44|提交申请;
-段少波|审批人|2025-07-30 10:06:19|同意|同意|;
-张成林|直接主管|2025-07-30 11:50:13|同意|;
-李锋|直接主管|2025-07-30 15:25:37|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:25:37|抄送</t>
+          <t>徐正亮|提交申请|2025-08-29 12:48:30|提交申请;
+徐正亮|2025-08-29 18:25:36|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1234,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FPYBksdcStKvBrQbfMBalQ06491753840309</t>
+          <t>eVaP5BzORdmX5JHoM-SVCw06491756432068</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1254,17 +1244,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-07-11 15:00</t>
+          <t>2025-08-29 13:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-07-11 17:30</t>
+          <t>2025-08-29 17:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>5小时</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1279,17 +1269,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>202507300951000497232</t>
+          <t>202508290947000488624</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-07-30 09:51:49</t>
+          <t>2025-08-29 09:47:49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>玉玲珑（魏玉玲）</t>
         </is>
       </c>
       <c r="L12"/>
@@ -1305,7 +1295,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-07-30 15:25:24</t>
+          <t>2025-08-29 15:02:11</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1315,26 +1305,26 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>玉玲珑（魏玉玲）提交的请假</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>段少波,张成林,李锋</t>
+          <t>李锋,张成林</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>5:33:36</t>
+          <t>5:14:23</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-30 09:51:49|提交申请;
-段少波|审批人|2025-07-30 10:06:31|同意|同意|;
-张成林|直接主管|2025-07-30 11:49:30|同意|;
-李锋|直接主管|2025-07-30 15:25:24|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 15:25:25|抄送</t>
+          <t>玉玲珑（魏玉玲）|提交申请|2025-08-29 09:47:48|提交申请;
+李锋|审批人|2025-08-29 10:35:12|同意|同意|;
+张成林|直接主管|2025-08-29 11:41:06|同意|;
+李锋|直接主管|2025-08-29 15:02:11|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-29 15:02:11|抄送</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1336,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fYYKoqHQQoyBuWdM6LVycQ06491753836458</t>
+          <t>J3v0PPd6SXyzYWqvBj_6Rg06491756430649</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1356,22 +1346,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-07-26 13:00</t>
+          <t>2025-09-05 08:30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-07-26 17:30</t>
+          <t>2025-09-06 18:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4.5小时</t>
+          <t>16小时</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>外婆离世，要去给外婆过五七。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1381,17 +1371,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>202507300847000381696</t>
+          <t>202508290924000092422</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-07-30 08:47:38</t>
+          <t>2025-08-29 09:24:09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>陈雄</t>
+          <t>夏天龙</t>
         </is>
       </c>
       <c r="L13"/>
@@ -1407,35 +1397,35 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-07-30 10:08:57</t>
+          <t>2025-08-29 11:41:33</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>试验科</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>陈雄提交的请假</t>
+          <t>夏天龙提交的请假</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>段少波,董磊</t>
+          <t>程志鹏,张成林</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1:21:18</t>
+          <t>2:17:24</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>陈雄|提交申请|2025-07-30 08:47:38|提交申请;
-段少波|审批人|2025-07-30 10:06:39|同意|同意|;
-董磊|直接主管|2025-07-30 10:08:57|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 10:08:57|抄送</t>
+          <t>夏天龙|提交申请|2025-08-29 09:24:09|提交申请;
+程志鹏|审批人|2025-08-29 10:33:50|同意|;
+张成林|审批人|2025-08-29 11:41:33|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-29 11:41:33|抄送</t>
         </is>
       </c>
     </row>
@@ -1447,32 +1437,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>xQPUFgdfQkeJZKrRX-hJ6A06491753836390</t>
+          <t>kdyhEjRgQhWQtz9X8xz2PA06491756423712</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-07-17 15:30</t>
+          <t>2025-08-28 上午</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-07-17 17:30</t>
+          <t>2025-08-29 下午</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>2天</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>腹部大面积过敏性皮炎 休息治疗</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1482,17 +1472,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>202507300846000300660</t>
+          <t>202508290728000327547</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-07-30 08:46:30</t>
+          <t>2025-08-29 07:28:33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>陈雄</t>
+          <t>葛婷</t>
         </is>
       </c>
       <c r="L14"/>
@@ -1508,35 +1498,35 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-07-30 10:09:06</t>
+          <t>2025-09-01 13:41:07</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>营销管理部</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>陈雄提交的请假</t>
+          <t>葛婷提交的请假</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>段少波,董磊</t>
+          <t>周哲敏</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1:22:36</t>
+          <t>78:12:34</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>陈雄|提交申请|2025-07-30 08:46:30|提交申请;
-段少波|审批人|2025-07-30 10:06:47|同意|同意|;
-董磊|直接主管|2025-07-30 10:09:06|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 10:09:07|抄送</t>
+          <t>葛婷|提交申请|2025-08-29 07:28:33|提交申请;
+周哲敏|审批人|2025-09-01 13:40:54|同意|同意|;
+周哲敏|直接主管|2025-09-01 13:41:07|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-01 13:41:07|抄送</t>
         </is>
       </c>
     </row>
@@ -1548,32 +1538,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>uN4RfHctRlCSCB3VesM_7w06491753836324</t>
+          <t>a6oIf9ElQq2r-1k2FkF-FA06491756371064</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-07-16 15:30</t>
+          <t>2025-08-28 上午</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-07-16 17:30</t>
+          <t>2025-08-28 下午</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>过敏性皮炎 休息治疗</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1583,61 +1573,59 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>202507300845000245003</t>
+          <t>202508281651000042088</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-07-30 08:45:24</t>
+          <t>2025-08-28 16:51:04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>陈雄</t>
+          <t>葛婷</t>
         </is>
       </c>
       <c r="L15"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-07-30 10:09:14</t>
+          <t>2025-08-28 16:51:04</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>营销管理部</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>陈雄提交的请假</t>
+          <t>葛婷提交的请假</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>段少波,董磊</t>
+          <t/>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1:23:50</t>
+          <t>14:36:41</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>陈雄|提交申请|2025-07-30 08:45:24|提交申请;
-段少波|审批人|2025-07-30 10:07:03|同意|同意|;
-董磊|直接主管|2025-07-30 10:09:14|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 10:09:14|抄送</t>
+          <t>葛婷|提交申请|2025-08-28 16:51:04|提交申请;
+葛婷|2025-08-29 07:27:46|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -1649,32 +1637,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-18cm1ExR9iD2-_tDTJpeA06491753836278</t>
+          <t>jUKnYSaGSkWeo2oZ4xZkmA06491756303315</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-07-15 15:00</t>
+          <t>2025-08-28 上午</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-07-15 17:30</t>
+          <t>2025-08-28 下午</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>感冒</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1684,17 +1672,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>202507300844000387656</t>
+          <t>202508272201000553012</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2025-07-30 08:44:38</t>
+          <t>2025-08-27 22:01:55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>陈雄</t>
+          <t>徐正亮</t>
         </is>
       </c>
       <c r="L16"/>
@@ -1710,35 +1698,35 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-07-30 10:09:22</t>
+          <t>2025-08-28 08:47:38</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>杭州劳务</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>陈雄提交的请假</t>
+          <t>徐正亮提交的请假</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>段少波,董磊</t>
+          <t>董磊,钟洪伟</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1:24:45</t>
+          <t>10:45:44</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>陈雄|提交申请|2025-07-30 08:44:38|提交申请;
-段少波|审批人|2025-07-30 10:07:15|同意|同意|;
-董磊|直接主管|2025-07-30 10:09:22|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 10:09:22|抄送</t>
+          <t>徐正亮|提交申请|2025-08-27 22:01:55|提交申请;
+钟洪伟|审批人|2025-08-28 08:41:57|同意|;
+董磊|审批人|2025-08-28 08:47:38|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-28 08:47:38|抄送</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1738,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tqE0yD_2QpaDO7OuK5WKGA06491753836216</t>
+          <t>9HTpX1o_Q2u0k5pilPRMyw06491756302520</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07-14 15:00</t>
+          <t>2025-08-27 下午</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-07-14 17:30</t>
+          <t>2025-08-27 下午</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.5小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>过敏磕完药，状态不太好</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1785,17 +1773,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>202507300843000367292</t>
+          <t>202508272148000406693</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-07-30 08:43:36</t>
+          <t>2025-08-27 21:48:40</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>陈雄</t>
+          <t>韦东略</t>
         </is>
       </c>
       <c r="L17"/>
@@ -1811,35 +1799,35 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2025-07-30 10:09:30</t>
+          <t>2025-08-29 10:00:10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>试验科</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>陈雄提交的请假</t>
+          <t>韦东略提交的请假</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>段少波,董磊</t>
+          <t>程志鹏,张成林</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1:25:54</t>
+          <t>36:11:29</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>陈雄|提交申请|2025-07-30 08:43:36|提交申请;
-段少波|审批人|2025-07-30 10:07:26|同意|同意|;
-董磊|直接主管|2025-07-30 10:09:30|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-30 10:09:30|抄送</t>
+          <t>韦东略|提交申请|2025-08-27 21:48:40|提交申请;
+程志鹏|审批人|2025-08-27 22:44:03|同意|;
+张成林|审批人|2025-08-29 10:00:10|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-29 10:00:10|抄送</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1839,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hHNH8uDxTGubtbb3zab6iQ06491753668413</t>
+          <t>zI4Km0k8QMmlrO741Y5WOw06491756281024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1861,12 +1849,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-07-28 11:30</t>
+          <t>2025-08-30 08:30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-07-28 18:00</t>
+          <t>2025-08-30 14:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1876,7 +1864,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>提车上牌</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1886,17 +1874,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>202507281006000534366</t>
+          <t>202508271550000246531</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-07-28 10:06:53</t>
+          <t>2025-08-27 15:50:24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L18"/>
@@ -1912,35 +1900,35 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-07-28 12:16:43</t>
+          <t>2025-08-28 07:55:35</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>张成林,程志鹏</t>
+          <t>杜鸣,张健宁</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2:9:50</t>
+          <t>16:5:11</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-28 10:06:53|提交申请;
-程志鹏|审批人|2025-07-28 10:08:11|同意|;
-张成林|审批人|2025-07-28 12:16:43|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-28 12:16:43|抄送</t>
+          <t>王兴磊|提交申请|2025-08-27 15:50:24|提交申请;
+张健宁|审批人|2025-08-27 21:41:57|同意|;
+杜鸣|直接主管|2025-08-28 07:55:35|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-28 07:55:35|抄送</t>
         </is>
       </c>
     </row>
@@ -1952,32 +1940,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qej94GLCSReTWEpzlen8og06491753501381</t>
+          <t>zyGqWtY0S2aVT7YiBIzZ7w06491756278502</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-07-26 13:00</t>
+          <t>2025-08-27 上午</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-07-26 17:30</t>
+          <t>2025-08-27 上午</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.5小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>晚上上小夜班，调休半天</t>
+          <t>生病</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1987,62 +1975,62 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>202507261143000018202</t>
+          <t>202508271508000224654</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-07-26 11:43:01</t>
+          <t>2025-08-27 15:08:22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>魏军</t>
-        </is>
-      </c>
-      <c r="L19"/>
+          <t>杨烜</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>石丁哲</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-07-26 17:21:24</t>
+          <t>2025-08-27 15:08:22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>AIO开发部</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>魏军提交的请假</t>
+          <t>杨烜提交的请假</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>张成林,李锋</t>
+          <t/>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>5:38:24</t>
+          <t>219:5:58</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>魏军|提交申请|2025-07-26 11:43:01|提交申请;
-李锋|审批人|2025-07-26 16:11:20|同意|同意|;
-张成林|直接主管|2025-07-26 16:50:21|同意|;
-李锋|直接主管|2025-07-26 17:21:24|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-26 17:21:24|抄送</t>
+          <t>杨烜|提交申请|2025-08-27 15:08:22|提交申请</t>
         </is>
       </c>
     </row>
@@ -2054,32 +2042,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>X6RR2CUDS6GpVAaSYJO4Nw06491753492103</t>
+          <t>J7gNf09nSLqcn8mlVvWUsw06491756252685</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-07-31 08:30</t>
+          <t>2025-08-27 上午</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-08-01 18:00</t>
+          <t>2025-08-27 下午</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>女朋友父母来杭州，带他们逛一下杭州</t>
+          <t>家中有事</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2089,61 +2077,62 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>202507260908000239155</t>
+          <t>202508270758000055949</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-07-26 09:08:23</t>
+          <t>2025-08-27 07:58:05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>夏天龙</t>
-        </is>
-      </c>
-      <c r="L20"/>
+          <t>陆尖</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>黄风丽</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-07-26 17:39:29</t>
+          <t>2025-08-27 07:58:05</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>夏天龙提交的请假</t>
+          <t>陆尖提交的请假</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t/>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>8:31:6</t>
+          <t>226:16:15</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>夏天龙|提交申请|2025-07-26 09:08:23|提交申请;
-程志鹏|审批人|2025-07-26 09:29:04|同意|;
-张成林|审批人|2025-07-26 17:39:29|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-26 17:39:30|抄送</t>
+          <t>陆尖|提交申请|2025-08-27 07:58:05|提交申请</t>
         </is>
       </c>
     </row>
@@ -2155,32 +2144,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>y3cmjHM2S86hPdWywGyF-g06491753451437</t>
+          <t>dTM8ksyqTgC4k1wkU7Z-qw06491756210522</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-07-28 08:30</t>
+          <t>2025-08-27 上午</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-07-28 18:00</t>
+          <t>2025-08-29 下午</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>3天</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>小孩快开学送回老家</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2190,62 +2179,64 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>202507252150000372049</t>
+          <t>202508262015000222801</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-07-25 21:50:37</t>
+          <t>2025-08-26 20:15:22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>周承成</t>
-        </is>
-      </c>
-      <c r="L21"/>
+          <t>梁校</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>李萍</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>审批中</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-07-27 09:53:05</t>
+          <t>2025-08-27 14:33:04</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>系统开发部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>周承成提交的请假</t>
+          <t>梁校提交的请假</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>朱显斌,雷继彬,林明山</t>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>36:2:29</t>
+          <t>237:58:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>周承成|提交申请|2025-07-25 21:50:37|提交申请;
-林明山|审批人|2025-07-26 16:36:44|同意|;
-朱显斌|直接主管|2025-07-26 22:37:48|同意|;
-雷继彬|审批人|2025-07-27 09:53:05|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-27 09:53:06|抄送</t>
+          <t>梁校|提交申请|2025-08-26 20:15:22|提交申请;
+钟洪伟|审批人|2025-08-27 14:30:47|同意|;
+董磊|直接主管|2025-08-27 14:33:04|同意|同意|</t>
         </is>
       </c>
     </row>
@@ -2257,32 +2248,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>utEu9tIDSsGtYDh0tglfiw06491753439508</t>
+          <t>zDhzXlgXSQu6N4WxxqZt2Q06491756207108</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-07-26 08:30</t>
+          <t>2025-08-26 上午</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-07-26 18:00</t>
+          <t>2025-08-26 上午</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>陪老婆去趟医院割阑尾</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2292,59 +2283,61 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>202507251831000481939</t>
+          <t>202508261918000284560</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-07-25 18:31:48</t>
+          <t>2025-08-26 19:18:28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>周承成</t>
+          <t>郑翔</t>
         </is>
       </c>
       <c r="L22"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2025-07-25 18:31:48</t>
+          <t>2025-08-28 10:01:03</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>系统开发部</t>
+          <t>信息与品宣部</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>周承成提交的请假</t>
+          <t>郑翔提交的请假</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t/>
+          <t>杜以烽</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0:23:2</t>
+          <t>38:42:35</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>周承成|提交申请|2025-07-25 18:31:48|提交申请;
-周承成|2025-07-25 18:54:51|终止流程实例</t>
+          <t>郑翔|提交申请|2025-08-26 19:18:28|提交申请;
+杜以烽|审批人|2025-08-28 10:00:59|同意|;
+杜以烽|直接主管|2025-08-28 10:01:03|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-28 10:01:04|抄送</t>
         </is>
       </c>
     </row>
@@ -2356,32 +2349,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>_hksq2NQSA2_fC2HikjbBw06491753435903</t>
+          <t>dCmQg9ErSWevbOEx2qhw4Q06491756207065</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-07-26 08:30</t>
+          <t>2025-08-26 上午</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-07-26 18:00</t>
+          <t>2025-08-26 上午</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>家里人生病，需去医院</t>
+          <t>陪老婆去趟医院</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2391,24 +2384,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>202507251731000439172</t>
+          <t>202508261917000451565</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2025-07-25 17:31:43</t>
+          <t>2025-08-26 19:17:45</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>葛婷</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>周哲敏</t>
-        </is>
-      </c>
+          <t>郑翔</t>
+        </is>
+      </c>
+      <c r="L23"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>--</t>
@@ -2416,39 +2405,38 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-07-26 17:55:41</t>
+          <t>2025-08-26 19:17:45</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>营销管理部</t>
+          <t>信息与品宣部</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>葛婷提交的请假</t>
+          <t>郑翔提交的请假</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>周哲敏,曾婷婷</t>
+          <t/>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>166:14:52</t>
+          <t>0:0:18</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>葛婷|提交申请|2025-07-25 17:31:43|提交申请;
-周哲敏|审批人|2025-07-26 17:52:54|转交|核算下之前有多少加班时间|;
-曾婷婷|审批人|2025-07-26 17:55:41|同意|6月份加班5小时，只可以调休5小时；剩余3小时按事假核算|</t>
+          <t>郑翔|提交申请|2025-08-26 19:17:45|提交申请;
+郑翔|2025-08-26 19:18:03|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -2460,32 +2448,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9vviBfEWS8iZYKxe61AISQ06491753433536</t>
+          <t>-m3xoO6aSWm8L_MUhGV85g06491756199268</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-07-26 08:30</t>
+          <t>2025-08-23 上午</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-07-26 17:30</t>
+          <t>2025-08-23 下午</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>调休一天，望批准</t>
+          <t>摔跤后右手撑地，手腕肿痛</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2495,17 +2483,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>202507251652000162208</t>
+          <t>202508261707000488453</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-07-25 16:52:16</t>
+          <t>2025-08-26 17:07:48</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>董凯宁</t>
+          <t>李俊杰</t>
         </is>
       </c>
       <c r="L24"/>
@@ -2521,36 +2509,35 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-07-26 09:12:58</t>
+          <t>2025-08-27 09:43:43</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>董凯宁提交的请假</t>
+          <t>李俊杰提交的请假</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>16:20:41</t>
+          <t>16:35:56</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>董凯宁|提交申请|2025-07-25 16:52:16|提交申请;
-李锋|审批人|2025-07-25 17:23:52|同意|同意|;
-张成林|直接主管|2025-07-26 08:59:34|同意|;
-李锋|直接主管|2025-07-26 09:12:58|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-26 09:12:58|抄送</t>
+          <t>李俊杰|提交申请|2025-08-26 17:07:48|提交申请;
+钟洪伟|审批人|2025-08-27 08:04:17|同意|;
+董磊|直接主管|2025-08-27 09:43:43|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-27 09:43:43|抄送</t>
         </is>
       </c>
     </row>
@@ -2562,32 +2549,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DBULaeduQFadirR3-Br8Cw06491753416274</t>
+          <t>dYTv96RmS6ywXD8yQLlqUw06491756168690</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-07-25 下午</t>
+          <t>2025-08-26 13:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-07-25 下午</t>
+          <t>2025-08-26 18:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.5天</t>
+          <t>5小时</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>小孩肚子疼</t>
+          <t>家中有事</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2597,17 +2584,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>202507251204000343047</t>
+          <t>202508260838000103200</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-07-25 12:04:34</t>
+          <t>2025-08-26 08:38:10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>梁校</t>
+          <t>钟洪伟</t>
         </is>
       </c>
       <c r="L25"/>
@@ -2623,35 +2610,35 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-07-27 19:15:40</t>
+          <t>2025-08-26 08:40:52</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>生产管理部,杭州劳务</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>梁校提交的请假</t>
+          <t>钟洪伟提交的请假</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>钟洪伟,董磊</t>
+          <t>董磊</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>55:11:6</t>
+          <t>0:2:42</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>梁校|提交申请|2025-07-25 12:04:34|提交申请;
-钟洪伟|审批人|2025-07-26 20:02:27|同意|;
-董磊|直接主管|2025-07-27 19:15:40|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-27 19:15:40|抄送</t>
+          <t>钟洪伟|提交申请|2025-08-26 08:38:10|提交申请;
+董磊|审批人|2025-08-26 08:40:26|同意|;
+董磊|直接主管|2025-08-26 08:40:52|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-26 08:40:52|抄送</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2650,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sQDPOyMQTaePVf1mOVH2CA06491753414419</t>
+          <t>po8zaUAXRkq2kCQhGgN9NQ06491756071035</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2673,12 +2660,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-07-26 上午</t>
+          <t>2025-08-25 上午</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-07-26 下午</t>
+          <t>2025-08-25 下午</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2688,7 +2675,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>家中有事</t>
+          <t>带小孩去医院看眼睛</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2698,62 +2685,61 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>202507251133000391293</t>
+          <t>202508250530000353101</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2025-07-25 11:33:39</t>
+          <t>2025-08-25 05:30:35</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>陆尖</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>黄风丽</t>
-        </is>
-      </c>
+          <t>梁校</t>
+        </is>
+      </c>
+      <c r="L26"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>审批中</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2025-07-25 11:33:39</t>
+          <t>2025-08-25 08:36:01</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>财务部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>陆尖提交的请假</t>
+          <t>梁校提交的请假</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t/>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>172:12:55</t>
+          <t>3:5:25</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>陆尖|提交申请|2025-07-25 11:33:39|提交申请</t>
+          <t>梁校|提交申请|2025-08-25 05:30:35|提交申请;
+钟洪伟|审批人|2025-08-25 08:23:04|同意|;
+董磊|直接主管|2025-08-25 08:36:01|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-25 08:36:01|抄送</t>
         </is>
       </c>
     </row>
@@ -2765,32 +2751,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0vtsevufQMGx3zB2DLe4sQ06491753238088</t>
+          <t>A8fDMEouQTCZQuyShZD51w06491756070797</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-07-24 上午</t>
+          <t>2025-08-25 08:30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-07-24 上午</t>
+          <t>2025-08-25 17:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.5天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>岳父家中有事。需要请半天假期。</t>
+          <t>带小孩去医院看眼睛</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2800,62 +2786,59 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>202507231034000481730</t>
+          <t>202508250526000376564</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-07-23 10:34:48</t>
+          <t>2025-08-25 05:26:37</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>陈登科</t>
+          <t>梁校</t>
         </is>
       </c>
       <c r="L27"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-07-23 15:03:49</t>
+          <t>2025-08-25 05:26:37</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>陈登科提交的请假</t>
+          <t>梁校提交的请假</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>张成林,李锋,段少波</t>
+          <t/>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>4:29:0</t>
+          <t>0:2:45</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>陈登科|提交申请|2025-07-23 10:34:48|提交申请;
-段少波|审批人|2025-07-23 10:36:28|同意|同意|;
-张成林|直接主管|2025-07-23 12:16:33|同意|;
-李锋|直接主管|2025-07-23 15:03:49|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-23 15:03:49|抄送</t>
+          <t>梁校|提交申请|2025-08-25 05:26:37|提交申请;
+梁校|2025-08-25 05:29:22|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -2867,32 +2850,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>c4mTGGoJQaaT5WTRy7UO_w06491753188955</t>
+          <t>5OpfZCMWRRGmrJZVvhudAA06491756028886</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-07-23 上午</t>
+          <t>2025-08-25 08:30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-07-23 下午</t>
+          <t>2025-08-25 17:30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>家里急事处理</t>
+          <t>周末加班调休一天</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2902,17 +2885,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>202507222055000557521</t>
+          <t>202508241748000063798</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2025-07-22 20:55:55</t>
+          <t>2025-08-24 17:48:06</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>叶文敬</t>
+          <t>李庭越</t>
         </is>
       </c>
       <c r="L28"/>
@@ -2928,35 +2911,35 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-07-23 08:42:36</t>
+          <t>2025-08-27 15:38:57</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>杭州劳务</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>叶文敬提交的请假</t>
+          <t>李庭越提交的请假</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>董磊,钟洪伟</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11:46:40</t>
+          <t>69:50:52</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>叶文敬|提交申请|2025-07-22 20:55:55|提交申请;
-钟洪伟|审批人|2025-07-23 08:42:06|同意|;
-董磊|审批人|2025-07-23 08:42:36|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-23 08:42:36|抄送</t>
+          <t>李庭越|提交申请|2025-08-24 17:48:06|提交申请;
+张健宁|审批人|2025-08-27 11:40:50|同意|;
+杜鸣|直接主管|2025-08-27 15:38:57|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-27 15:38:57|抄送</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2951,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PfRI4AF-RbSkdN2ham22xQ06491753152927</t>
+          <t>BqFQXCKzSAWb57Tnvwo03Q06491756018257</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2978,22 +2961,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-07-28 08:30</t>
+          <t>2025-08-25 08:30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-07-29 17:30</t>
+          <t>2025-08-25 18:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16小时</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>有事情需要处理，故调休两天</t>
+          <t>调休一天； 
+订机票送老婆去（南京）机场回豫返郑。
+用：8月1日、8月8日、8月15日 有效加班累计8.3小时调休使用。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3003,17 +2988,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>202507221055000275563</t>
+          <t>202508241450000577431</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-07-22 10:55:27</t>
+          <t>2025-08-24 14:50:57</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>黄力</t>
+          <t>高剑濠</t>
         </is>
       </c>
       <c r="L29"/>
@@ -3029,35 +3014,35 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2025-07-28 08:21:54</t>
+          <t>2025-08-25 11:51:44</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>试验科</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>黄力提交的请假</t>
+          <t>高剑濠提交的请假</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>张健宁,杜鸣</t>
+          <t>张成林,程志鹏</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>141:26:27</t>
+          <t>21:0:47</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>黄力|提交申请|2025-07-22 10:55:27|提交申请;
-张健宁|审批人|2025-07-27 15:50:00|同意|加班部分抵充调休，不足部分按事假处理|;
-杜鸣|直接主管|2025-07-28 08:21:54|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-28 08:21:54|抄送</t>
+          <t>高剑濠|提交申请|2025-08-24 14:50:57|提交申请;
+程志鹏|审批人|2025-08-25 11:18:39|同意|;
+张成林|审批人|2025-08-25 11:51:44|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-25 11:51:44|抄送</t>
         </is>
       </c>
     </row>
@@ -3069,32 +3054,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>oT4MSgKqRsOsJdAN3p1AWg06491753146092</t>
+          <t>MHSFMVRdTZOgkQsOKD8XcQ06491755919672</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-07-28 08:30</t>
+          <t>2025-08-23 上午</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-07-28 17:30</t>
+          <t>2025-08-23 下午</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>有事情处理需调休一天</t>
+          <t>有事</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3104,59 +3089,61 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>202507220901000325844</t>
+          <t>202508231127000521166</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-07-22 09:01:32</t>
+          <t>2025-08-23 11:27:52</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>黄力</t>
+          <t>陆尖</t>
         </is>
       </c>
       <c r="L30"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2025-07-22 09:01:32</t>
+          <t>2025-09-03 09:20:27</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>黄力提交的请假</t>
+          <t>陆尖提交的请假</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t/>
+          <t>黄风丽</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1:50:3</t>
+          <t>261:52:36</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>黄力|提交申请|2025-07-22 09:01:32|提交申请;
-黄力|2025-07-22 10:51:36|终止流程实例</t>
+          <t>陆尖|提交申请|2025-08-23 11:27:52|提交申请;
+黄风丽|审批人|2025-09-03 09:19:06|同意|同意|;
+黄风丽|直接主管|2025-09-03 09:20:27|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-03 09:20:27|抄送</t>
         </is>
       </c>
     </row>
@@ -3168,32 +3155,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3o-mqPFNRe27Ry7oyru8WQ06491753143910</t>
+          <t>ebE1QwwyQWy7-k10m4TjtQ06491755902879</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-07-22 08:30</t>
+          <t>2025-08-23 上午</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-07-22 13:00</t>
+          <t>2025-08-23 下午</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>处理一些事情</t>
+          <t>有事</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3203,17 +3190,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>202507220825000107922</t>
+          <t>202508230647000592698</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-07-22 08:25:10</t>
+          <t>2025-08-23 06:47:59</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>韦东略</t>
+          <t>白敏娟</t>
         </is>
       </c>
       <c r="L31"/>
@@ -3229,35 +3216,35 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2025-07-23 08:48:52</t>
+          <t>2025-08-26 11:51:24</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>供应链管理部</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>韦东略提交的请假</t>
+          <t>白敏娟提交的请假</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>陈虞涛</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>24:23:43</t>
+          <t>77:3:26</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>韦东略|提交申请|2025-07-22 08:25:10|提交申请;
-程志鹏|审批人|2025-07-23 08:35:05|同意|;
-张成林|审批人|2025-07-23 08:48:52|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-23 08:48:52|抄送</t>
+          <t>白敏娟|提交申请|2025-08-23 06:47:59|提交申请;
+陈虞涛|审批人|2025-08-26 11:50:40|同意|;
+陈虞涛|直接主管|2025-08-26 11:51:24|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-26 11:51:25|抄送</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3256,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>h4FyZzPFTTWjYMO-DSGtcQ06491752918412</t>
+          <t>UhnVPn8HTpiaXSjL62HrNg06491755874499</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3279,12 +3266,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-07-19 08:30</t>
+          <t>2025-08-23 08:30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-07-19 17:30</t>
+          <t>2025-08-23 18:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3294,7 +3281,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>生产休息 调休</t>
+          <t>家中有事</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3304,17 +3291,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>202507191746000522205</t>
+          <t>202508222254000596471</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-07-19 17:46:52</t>
+          <t>2025-08-22 22:54:59</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>玉玲珑（魏玉玲）</t>
+          <t>贾敏洋</t>
         </is>
       </c>
       <c r="L32"/>
@@ -3330,36 +3317,35 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2025-07-20 21:51:13</t>
+          <t>2025-09-03 09:20:13</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>财务部</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>玉玲珑（魏玉玲）提交的请假</t>
+          <t>贾敏洋提交的请假</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>黄风丽</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>28:4:21</t>
+          <t>274:25:15</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>玉玲珑（魏玉玲）|提交申请|2025-07-19 17:46:52|提交申请;
-李锋|审批人|2025-07-20 09:40:15|同意|同意|;
-张成林|直接主管|2025-07-20 21:37:48|同意|;
-李锋|直接主管|2025-07-20 21:51:13|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-20 21:51:13|抄送</t>
+          <t>贾敏洋|提交申请|2025-08-22 22:54:59|提交申请;
+黄风丽|审批人|2025-09-03 09:19:20|同意|同意|;
+黄风丽|直接主管|2025-09-03 09:20:13|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-09-03 09:20:13|抄送</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3357,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vSWHwuZ4QVOoQV9KxbTg2w06491752889545</t>
+          <t>2KBypG_BRZC5vxjQrwQmGw06491755856935</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3381,12 +3367,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-07-19 08:30</t>
+          <t>2025-08-23 08:30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-07-19 17:30</t>
+          <t>2025-08-23 17:30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3396,7 +3382,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>车间休息</t>
+          <t>累计调休</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3406,17 +3392,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>202507190945000457098</t>
+          <t>202508221802000163500</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2025-07-19 09:45:45</t>
+          <t>2025-08-22 18:02:16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>殷四雄</t>
         </is>
       </c>
       <c r="L33"/>
@@ -3432,7 +3418,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2025-07-20 21:50:49</t>
+          <t>2025-08-22 20:45:29</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3442,7 +3428,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>刘洋提交的请假</t>
+          <t>殷四雄提交的请假</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3452,16 +3438,16 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>36:5:3</t>
+          <t>2:43:14</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>刘洋|提交申请|2025-07-19 09:45:45|提交申请;
-李锋|审批人|2025-07-19 10:26:41|同意|同意|;
-张成林|直接主管|2025-07-20 21:38:04|同意|;
-李锋|直接主管|2025-07-20 21:50:49|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-20 21:50:49|抄送</t>
+          <t>殷四雄|提交申请|2025-08-22 18:02:16|提交申请;
+李锋|审批人|2025-08-22 18:16:33|同意|同意|;
+张成林|直接主管|2025-08-22 19:53:02|同意|;
+李锋|直接主管|2025-08-22 20:45:29|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-22 20:45:29|抄送</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3459,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fokJ1Rk-SPSCw5rcTLUQrA06491752884837</t>
+          <t>25WnuXzgQ6C0PlJzSMgAkQ06491755840271</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3483,22 +3469,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-07-19 08:30</t>
+          <t>2025-08-28 08:30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-07-19 17:30</t>
+          <t>2025-08-29 17:30</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>16小时</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>生产休息，调休一天</t>
+          <t>加班时长过多调休两天！</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3508,17 +3494,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>202507190827000178179</t>
+          <t>202508221324000319850</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2025-07-19 08:27:17</t>
+          <t>2025-08-22 13:24:31</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>魏军</t>
+          <t>李庭越</t>
         </is>
       </c>
       <c r="L34"/>
@@ -3534,36 +3520,35 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2025-07-20 21:51:03</t>
+          <t>2025-08-26 08:17:57</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>魏军提交的请假</t>
+          <t>李庭越提交的请假</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>37:23:46</t>
+          <t>90:53:27</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>魏军|提交申请|2025-07-19 08:27:17|提交申请;
-李锋|审批人|2025-07-19 10:26:53|同意|同意|;
-张成林|直接主管|2025-07-20 21:37:55|同意|;
-李锋|直接主管|2025-07-20 21:51:03|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-20 21:51:04|抄送</t>
+          <t>李庭越|提交申请|2025-08-22 13:24:31|提交申请;
+张健宁|审批人|2025-08-23 19:19:42|同意|;
+杜鸣|直接主管|2025-08-26 08:17:57|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-26 08:17:57|抄送</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3560,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FqI4VDJHQvCMvsi-6px63w06491752834159</t>
+          <t>7sMeWWUIQOmJf9UH6IuBtw06491755828976</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3585,12 +3570,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-07-19 08:30</t>
+          <t>2025-08-23 08:30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-07-19 17:30</t>
+          <t>2025-08-23 17:30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3600,7 +3585,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3610,17 +3595,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>202507181822000398830</t>
+          <t>202508221016000164206</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-07-18 18:22:39</t>
+          <t>2025-08-22 10:16:16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>张曙光</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L35"/>
@@ -3636,36 +3621,35 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2025-07-20 21:50:33</t>
+          <t>2025-08-26 08:18:12</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>张曙光提交的请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>51:27:54</t>
+          <t>94:1:57</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>张曙光|提交申请|2025-07-18 18:22:39|提交申请;
-李锋|审批人|2025-07-18 18:51:33|同意|同意|;
-张成林|直接主管|2025-07-20 21:38:17|同意|;
-李锋|直接主管|2025-07-20 21:50:33|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-20 21:50:33|抄送</t>
+          <t>王兴磊|提交申请|2025-08-22 10:16:16|提交申请;
+张健宁|审批人|2025-08-23 19:19:37|同意|;
+杜鸣|直接主管|2025-08-26 08:18:12|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-26 08:18:12|抄送</t>
         </is>
       </c>
     </row>
@@ -3677,32 +3661,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>n2smQgWzREiKMn2yovCfSA06491752794897</t>
+          <t>By8i3UKvTciFmjLj66vrrA06491755746518</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07-18 AM</t>
+          <t>2025-08-22 08:30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-07-18 AM</t>
+          <t>2025-08-22 17:30</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.5天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">吹空调导致身体不舒服 </t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3712,61 +3696,59 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>202507180728000179618</t>
+          <t>202508211121000582205</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2025-07-18 07:28:17</t>
+          <t>2025-08-21 11:21:58</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>左山林</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L36"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2025-07-18 16:17:26</t>
+          <t>2025-08-21 11:21:58</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>信息与品宣部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>左山林's 请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>张世丽,杜以烽</t>
+          <t/>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>8:49:10</t>
+          <t>4:32:24</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>左山林|submit application|2025-07-18 07:28:17|提交申请;
-张世丽|审批人|2025-07-18 08:20:44|同意|同意|;
-杜以烽|直接主管|2025-07-18 16:17:26|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-18 16:17:26|抄送</t>
+          <t>王兴磊|提交申请|2025-08-21 11:21:58|提交申请;
+王兴磊|2025-08-21 15:54:22|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3760,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>iFAazCZFTtuMfoyfzUb-iw06491752743999</t>
+          <t>CMJs5Q0vRnCcuCTI46wjXQ06491755744438</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3788,12 +3770,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-07-18 08:25</t>
+          <t>2025-08-23 08:30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-07-18 17:31</t>
+          <t>2025-08-23 17:30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3803,7 +3785,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>累计加班调休</t>
+          <t>家中有事</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3813,17 +3795,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>202507171719000593180</t>
+          <t>202508211047000182710</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2025-07-17 17:19:59</t>
+          <t>2025-08-21 10:47:18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>马鸣强</t>
+          <t>陈登科</t>
         </is>
       </c>
       <c r="L37"/>
@@ -3839,7 +3821,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2025-07-18 07:19:54</t>
+          <t>2025-08-22 18:16:47</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3849,26 +3831,26 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>马鸣强提交的请假</t>
+          <t>陈登科提交的请假</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>张成林,李锋</t>
+          <t>段少波,张成林,李锋</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>13:59:56</t>
+          <t>31:29:29</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>马鸣强|提交申请|2025-07-17 17:19:59|提交申请;
-李锋|审批人|2025-07-17 18:17:09|同意|同意|;
-张成林|直接主管|2025-07-17 22:46:16|同意|;
-李锋|直接主管|2025-07-18 07:19:54|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-18 07:19:54|抄送</t>
+          <t>陈登科|提交申请|2025-08-21 10:47:18|提交申请;
+段少波|审批人|2025-08-22 15:14:43|同意|同意|;
+张成林|直接主管|2025-08-22 15:35:05|同意|;
+李锋|直接主管|2025-08-22 18:16:47|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-22 18:16:48|抄送</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3862,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N-RhbbysQW-KYNtHCYRWnw06491752743617</t>
+          <t>OMt8lEXcTfeB0ZVAAovBHA06491755684068</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3890,22 +3872,23 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-07-18 08:30</t>
+          <t>2025-08-22 08:30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-07-18 17:30</t>
+          <t>2025-08-23 18:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>16小时</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>调休一天，望批准</t>
+          <t>调休；因本人老婆暑期放假从河南洛阳来杭州看望我，故而申请调休出去旅游。
+*用  6月17日、7月2日、7月9日、7月14日、7月15日、7月25日  累计有效加班时长16小时使用！</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3915,17 +3898,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>202507171713000371352</t>
+          <t>202508201801000087307</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2025-07-17 17:13:37</t>
+          <t>2025-08-20 18:01:08</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>董凯宁</t>
+          <t>高剑濠</t>
         </is>
       </c>
       <c r="L38"/>
@@ -3941,36 +3924,35 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2025-07-18 07:20:10</t>
+          <t>2025-08-21 08:43:55</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>试验科</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>董凯宁提交的请假</t>
+          <t>高剑濠提交的请假</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>程志鹏,张成林</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>14:6:33</t>
+          <t>14:42:48</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>董凯宁|提交申请|2025-07-17 17:13:37|提交申请;
-李锋|审批人|2025-07-17 18:17:29|同意|同意|;
-张成林|直接主管|2025-07-17 22:46:11|同意|;
-李锋|直接主管|2025-07-18 07:20:10|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-18 07:20:10|抄送</t>
+          <t>高剑濠|提交申请|2025-08-20 18:01:08|提交申请;
+程志鹏|审批人|2025-08-20 21:09:59|同意|;
+张成林|审批人|2025-08-21 08:43:55|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-21 08:43:55|抄送</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3964,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FyRCqN6AQ4CNI7Lsl7DcDQ06491752722492</t>
+          <t>Ozq7r9x3SPWxwdajnH2kjw06491755679708</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3992,22 +3974,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-07-17 11:30</t>
+          <t>2025-08-18 08:30</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-07-17 18:00</t>
+          <t>2025-08-18 12:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5小时</t>
+          <t>3.5小时</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>科目一考试，用7.12和7.16调休</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4017,17 +3999,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>202507171121000320099</t>
+          <t>202508201648000284664</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2025-07-17 11:21:32</t>
+          <t>2025-08-20 16:48:28</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L39"/>
@@ -4043,35 +4025,36 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2025-07-17 22:46:21</t>
+          <t>2025-08-21 22:46:44</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>陈雄提交的请假</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>段少波,张成林,李锋</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>11:24:49</t>
+          <t>29:58:16</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-17 11:21:32|提交申请;
-程志鹏|审批人|2025-07-17 11:24:52|同意|;
-张成林|审批人|2025-07-17 22:46:21|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-17 22:46:21|抄送</t>
+          <t>陈雄|提交申请|2025-08-20 16:48:28|提交申请;
+段少波|审批人|2025-08-21 09:21:57|同意|同意|;
+张成林|直接主管|2025-08-21 20:15:50|同意|;
+李锋|直接主管|2025-08-21 22:46:44|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-21 22:46:44|抄送</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4066,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>f_9-WJUYRqaH7Xlbo0jnTA06491752722395</t>
+          <t>JaOgwGcVRqaf1gjpMz7UIg06491755589929</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4093,22 +4076,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-07-24 12:00</t>
+          <t>2025-08-19 15:30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-07-24 18:30</t>
+          <t>2025-08-19 17:30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5小时</t>
+          <t>2小时</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>临时有事调休2小时</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4118,17 +4101,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>202507171119000552594</t>
+          <t>202508191552000098471</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-07-17 11:19:55</t>
+          <t>2025-08-19 15:52:09</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>贾海泉</t>
+          <t>李庭越</t>
         </is>
       </c>
       <c r="L40"/>
@@ -4144,35 +4127,35 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2025-07-21 20:43:06</t>
+          <t>2025-08-22 08:33:01</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>行政部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>贾海泉提交的请假</t>
+          <t>李庭越提交的请假</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>尹娜</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>105:23:12</t>
+          <t>64:40:52</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>贾海泉|提交申请|2025-07-17 11:19:55|提交申请;
-尹娜|审批人|2025-07-18 10:21:59|同意|;
-尹娜|直接主管|2025-07-21 20:43:06|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-21 20:43:06|抄送</t>
+          <t>李庭越|提交申请|2025-08-19 15:52:09|提交申请;
+张健宁|审批人|2025-08-22 08:16:07|同意|;
+杜鸣|直接主管|2025-08-22 08:33:01|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-22 08:33:01|抄送</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4167,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9Ui4PMyiR-OImJ59J9TQJg06491752643802</t>
+          <t>QVXgPiQhSTSPwtdepbMu1w06491755576472</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4194,12 +4177,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-07-16 上午</t>
+          <t>2025-08-19 下午</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-07-16 上午</t>
+          <t>2025-08-19 下午</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4209,7 +4192,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>起来时头昏</t>
+          <t>有事</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4219,17 +4202,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>202507161330000021095</t>
+          <t>202508191207000526594</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-07-16 13:30:02</t>
+          <t>2025-08-19 12:07:52</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>袁俊祥</t>
+          <t>白敏娟</t>
         </is>
       </c>
       <c r="L41"/>
@@ -4245,35 +4228,35 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-07-18 16:18:31</t>
+          <t>2025-08-26 11:51:07</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>信息与品宣部</t>
+          <t>供应链管理部</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>袁俊祥提交的请假</t>
+          <t>白敏娟提交的请假</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>杜以烽</t>
+          <t>陈虞涛</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>50:48:29</t>
+          <t>167:43:16</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>袁俊祥|提交申请|2025-07-16 13:30:02|提交申请;
-杜以烽|审批人|2025-07-18 16:17:37|同意|;
-杜以烽|直接主管|2025-07-18 16:18:31|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-18 16:18:31|抄送</t>
+          <t>白敏娟|提交申请|2025-08-19 12:07:52|提交申请;
+陈虞涛|审批人|2025-08-26 11:50:52|同意|;
+陈虞涛|直接主管|2025-08-26 11:51:07|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-26 11:51:07|抄送</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4268,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>iwWWNU5DR-a9myHxN1ThOA06491752635744</t>
+          <t>GBDReVMeQJuwpXakG756ZA06491755563335</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>病假</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-07-16 13:00</t>
+          <t>2025-08-19 上午</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-07-16 17:30</t>
+          <t>2025-08-19 下午</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>调休半天</t>
+          <t>身体不适</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4320,17 +4303,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>202507161115000446473</t>
+          <t>202508190828000552415</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-07-16 11:15:44</t>
+          <t>2025-08-19 08:28:55</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>王兴磊</t>
+          <t>朱强</t>
         </is>
       </c>
       <c r="L42"/>
@@ -4346,35 +4329,35 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2025-07-18 11:04:55</t>
+          <t>2025-08-19 10:15:45</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>生产管理部</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>王兴磊提交的请假</t>
+          <t>朱强提交的请假</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>张健宁,杜鸣</t>
+          <t>钟洪伟,董磊</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>47:49:11</t>
+          <t>1:46:50</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>王兴磊|提交申请|2025-07-16 11:15:44|提交申请;
-张健宁|审批人|2025-07-18 07:26:41|同意|;
-杜鸣|直接主管|2025-07-18 11:04:55|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-18 11:04:55|抄送</t>
+          <t>朱强|提交申请|2025-08-19 08:28:55|提交申请;
+钟洪伟|审批人|2025-08-19 09:53:09|同意|;
+董磊|直接主管|2025-08-19 10:15:45|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-19 10:15:45|抄送</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4369,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IuLki9b1SvO5_2EWS2P1kQ06491752576062</t>
+          <t>Vvp8T7i6S0yLr5_GgpG94A06491755501030</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4396,22 +4379,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-16 08:30</t>
+          <t>2025-08-08 08:30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-07-16 10:30</t>
+          <t>2025-08-08 17:30</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>由于咳嗽去医院配个药</t>
+          <t>通宵调休</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4421,17 +4404,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>202507151841000028735</t>
+          <t>202508181510000303437</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-07-15 18:41:02</t>
+          <t>2025-08-18 15:10:30</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>夏天龙</t>
+          <t>陈登科</t>
         </is>
       </c>
       <c r="L43"/>
@@ -4447,35 +4430,36 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2025-07-16 10:06:15</t>
+          <t>2025-08-18 16:15:24</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>夏天龙提交的请假</t>
+          <t>陈登科提交的请假</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>段少波,张成林,李锋</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15:25:14</t>
+          <t>1:4:53</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>夏天龙|提交申请|2025-07-15 18:41:02|提交申请;
-程志鹏|审批人|2025-07-16 08:35:48|同意|;
-张成林|审批人|2025-07-16 10:06:15|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-16 10:06:16|抄送</t>
+          <t>陈登科|提交申请|2025-08-18 15:10:30|提交申请;
+段少波|审批人|2025-08-18 15:14:08|同意|同意|;
+张成林|直接主管|2025-08-18 16:10:07|同意|;
+李锋|直接主管|2025-08-18 16:15:24|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-18 16:15:24|抄送</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4471,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PFrUIq_YRFqVIS5rg1c3wg06491752221908</t>
+          <t>bXC4Fzw2TByQMlYdikYxqg06491755497639</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4497,12 +4481,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-07-12 08:30</t>
+          <t>2025-08-16 08:30</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-07-12 17:30</t>
+          <t>2025-08-16 17:30</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4512,7 +4496,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>调休一天，望批准</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4522,17 +4506,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>202507111618000284947</t>
+          <t>202508181413000593425</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-07-11 16:18:28</t>
+          <t>2025-08-18 14:13:59</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>董凯宁</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L44"/>
@@ -4548,7 +4532,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2025-07-12 08:14:46</t>
+          <t>2025-08-18 16:15:13</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4558,26 +4542,26 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>董凯宁提交的请假</t>
+          <t>陈雄提交的请假</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t>张成林,李锋,段少波</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>15:56:18</t>
+          <t>2:1:15</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>董凯宁|提交申请|2025-07-11 16:18:28|提交申请;
-李锋|审批人|2025-07-11 18:57:51|同意|同意|;
-张成林|直接主管|2025-07-11 20:17:07|同意|;
-李锋|直接主管|2025-07-12 08:14:46|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-12 08:14:46|抄送</t>
+          <t>陈雄|提交申请|2025-08-18 14:13:59|提交申请;
+段少波|审批人|2025-08-18 15:15:16|同意|同意|;
+张成林|直接主管|2025-08-18 16:10:32|同意|;
+李锋|直接主管|2025-08-18 16:15:13|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-18 16:15:14|抄送</t>
         </is>
       </c>
     </row>
@@ -4589,52 +4573,52 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FQweVlPSST-2zFuA7WhpXw06491752138328</t>
+          <t>18oD823nTWuyK2GfLa9Fpw06491755488941</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-07-12 上午</t>
+          <t>2025-08-18 13:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-07-12 下午</t>
+          <t>2025-08-18 17:30</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>5小时</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>就医（口腔正畸检查）</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPD3zK_geFdbnNBP_NAj-w-l-5ze_OT0kIToFphsdMAA_575_1279.jpg</t>
+          <t/>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>202507101705000289005</t>
+          <t>202508181149000012027</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-07-10 17:05:28</t>
+          <t>2025-08-18 11:49:01</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>高嘉泽</t>
+          <t>玉玲珑（魏玉玲）</t>
         </is>
       </c>
       <c r="L45"/>
@@ -4650,35 +4634,36 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2025-07-11 13:37:49</t>
+          <t>2025-08-18 17:47:18</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>信息与品宣部</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>高嘉泽提交的请假</t>
+          <t>玉玲珑（魏玉玲）提交的请假</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>杜以烽,张世丽</t>
+          <t>张成林,李锋</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>20:32:22</t>
+          <t>5:58:17</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>高嘉泽|提交申请|2025-07-10 17:05:28|提交申请;
-张世丽|审批人|2025-07-10 17:52:56|同意|同意|;
-杜以烽|直接主管|2025-07-11 13:37:49|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-11 13:37:49|抄送</t>
+          <t>玉玲珑（魏玉玲）|提交申请|2025-08-18 11:49:01|提交申请;
+李锋|审批人|2025-08-18 16:15:35|同意|同意|;
+张成林|直接主管|2025-08-18 16:21:33|同意|;
+李锋|直接主管|2025-08-18 17:47:18|同意|确认|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-18 17:47:18|抄送</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4675,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>xFNFjj2KQke0qMOeW4wYcw06491752131614</t>
+          <t>htwqJWFFT-61k3rQcMe6Qg06491755256534</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4700,12 +4685,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-07-11 08:30</t>
+          <t>2025-08-16 08:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-07-11 17:30</t>
+          <t>2025-08-16 17:30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4715,7 +4700,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4725,12 +4710,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>202507101513000340800</t>
+          <t>202508151915000349894</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2025-07-10 15:13:34</t>
+          <t>2025-08-15 19:15:34</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4751,7 +4736,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2025-07-11 09:13:05</t>
+          <t>2025-08-19 08:23:35</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4771,15 +4756,15 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>17:59:32</t>
+          <t>85:8:0</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>王兴磊|提交申请|2025-07-10 15:13:34|提交申请;
-张健宁|审批人|2025-07-11 08:48:40|同意|;
-杜鸣|直接主管|2025-07-11 09:13:05|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-11 09:13:05|抄送</t>
+          <t>王兴磊|提交申请|2025-08-15 19:15:34|提交申请;
+张健宁|审批人|2025-08-18 18:32:12|同意|;
+杜鸣|直接主管|2025-08-19 08:23:35|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-19 08:23:35|抄送</t>
         </is>
       </c>
     </row>
@@ -4791,32 +4776,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>vzalzV4KQdaEWZLEym1xrw06491752121263</t>
+          <t>KbZc5JZ4SYGWY083MQlyeA06491755217782</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-07-11 上午</t>
+          <t>2025-08-15 08:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-07-11 下午</t>
+          <t>2025-08-15 09:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>1小时</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>在老家，11号下午到杭州</t>
+          <t>儿子考试！老妈电瓶车坏了！送他们过去！路上有点堵！</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4826,17 +4811,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>202507101221000038651</t>
+          <t>202508150829000429167</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2025-07-10 12:21:03</t>
+          <t>2025-08-15 08:29:42</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>梁校</t>
+          <t>朱强</t>
         </is>
       </c>
       <c r="L47"/>
@@ -4852,7 +4837,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2025-07-10 14:01:39</t>
+          <t>2025-08-19 10:14:31</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4862,7 +4847,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>梁校提交的请假</t>
+          <t>朱强提交的请假</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4872,15 +4857,15 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1:40:36</t>
+          <t>97:44:49</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>梁校|提交申请|2025-07-10 12:21:03|提交申请;
-钟洪伟|审批人|2025-07-10 12:21:34|同意|;
-董磊|直接主管|2025-07-10 14:01:39|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-10 14:01:39|抄送</t>
+          <t>朱强|提交申请|2025-08-15 08:29:42|提交申请;
+钟洪伟|审批人|2025-08-19 09:54:05|同意|;
+董磊|直接主管|2025-08-19 10:14:31|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-19 10:14:31|抄送</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4877,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7YYnN6jXQCW5LFNCS-Vfpg06491752019740</t>
+          <t>YvwW44EqRe24owp1WCXmTQ06491755163549</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4902,22 +4887,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-07-17 08:00</t>
+          <t>2025-08-15 08:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-07-18 19:30</t>
+          <t>2025-08-15 17:30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>16小时</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5月份加班剩余2.5天未调休，6月加班三天（6.1/6.7/6.21）未调休。共计5.5天。本次调休后剩余3.5天。</t>
+          <t>加班抵调休</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4927,17 +4912,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>202507090809000004156</t>
+          <t>202508141725000494255</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2025-07-09 08:09:00</t>
+          <t>2025-08-14 17:25:49</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>王进</t>
+          <t>沈琪海</t>
         </is>
       </c>
       <c r="L48"/>
@@ -4953,35 +4938,35 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2025-07-09 13:33:10</t>
+          <t>2025-08-19 08:22:56</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>售后服务部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>王进提交的请假</t>
+          <t>沈琪海提交的请假</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>张成林</t>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>5:24:11</t>
+          <t>110:57:7</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>王进|提交申请|2025-07-09 08:09:00|提交申请;
-张成林|审批人|2025-07-09 13:33:00|同意|;
-张成林|直接主管|2025-07-09 13:33:10|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-09 13:33:10|抄送</t>
+          <t>沈琪海|提交申请|2025-08-14 17:25:49|提交申请;
+张健宁|审批人|2025-08-18 18:32:50|同意|;
+杜鸣|直接主管|2025-08-19 08:22:56|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-19 08:22:56|抄送</t>
         </is>
       </c>
     </row>
@@ -4993,52 +4978,52 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>u9XEOTqjRA6UMKOb4yrH-g06491751890043</t>
+          <t>WgXGcWXmSxySzgZuLlZb8w06491755049026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>丧假</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-07-07 上午</t>
+          <t>2025-08-01 上午</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-07-07 下午</t>
+          <t>2025-08-05 下午</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>3天</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高烧，肺炎</t>
+          <t>婆婆去世，处理后事，原飞书202508040001请假作废</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPD3JsLWYOCm3NBiTNBJywiKaNZceBREAISkkEoK-WAA_1180_1572.jpg</t>
+          <t>https://static.dingtalk.com/media/lQDPM48BnxxHv63NBQDNA66weHg26DSzOMUIeeLQR0kxAA_942_1280.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>202507072007000237218</t>
+          <t>202508130937000065866</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2025-07-07 20:07:23</t>
+          <t>2025-08-13 09:37:06</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>梁梅</t>
         </is>
       </c>
       <c r="L49"/>
@@ -5054,35 +5039,36 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2025-07-09 13:33:42</t>
+          <t>2025-08-25 14:25:29</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>梁梅提交的请假</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>张成林,程志鹏</t>
+          <t>张健宁,杜鸣,李萍</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>41:26:19</t>
+          <t>292:48:23</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-07 20:07:23|提交申请;
-程志鹏|审批人|2025-07-07 20:47:27|同意|;
-张成林|审批人|2025-07-09 13:33:42|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-09 13:33:42|抄送</t>
+          <t>梁梅|提交申请|2025-08-13 09:37:06|提交申请;
+张健宁|审批人|2025-08-18 18:33:03|同意|;
+杜鸣|直接主管|2025-08-19 08:22:33|同意|;
+李萍|审批人|2025-08-25 14:25:29|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-25 14:25:29|抄送</t>
         </is>
       </c>
     </row>
@@ -5094,32 +5080,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9EUidOWBSAOkUMwqBziu3A06491751869507</t>
+          <t>H5CElJJYRyiP5abl0Nfadw06491754960412</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>事假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-07-08 上午</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-07-08 下午</t>
+          <t>2025-08-11 17:30</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>家中有事请假一天，望领导们批准</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5129,59 +5115,62 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>202507071425000072512</t>
+          <t>202508120900000121534</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2025-07-07 14:25:07</t>
+          <t>2025-08-12 09:00:12</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>李庭越</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L50"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2025-07-07 14:25:07</t>
+          <t>2025-08-12 14:59:45</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>李庭越提交的请假</t>
+          <t>陈雄提交的请假</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t/>
+          <t>张成林,李锋,段少波</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3:3:8</t>
+          <t>5:59:33</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>李庭越|提交申请|2025-07-07 14:25:07|提交申请;
-李庭越|2025-07-07 17:28:16|终止流程实例</t>
+          <t>陈雄|提交申请|2025-08-12 09:00:12|提交申请;
+段少波|审批人|2025-08-12 09:03:34|同意|同意|;
+张成林|直接主管|2025-08-12 14:22:23|同意|;
+李锋|直接主管|2025-08-12 14:59:45|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-12 14:59:46|抄送</t>
         </is>
       </c>
     </row>
@@ -5193,52 +5182,52 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ku4d92wRQo-UdicyMSvRFg06491751862954</t>
+          <t>1ltMYAvQQaG04vdDP8Tc4Q06491754959956</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-07-07 上午</t>
+          <t>2025-08-08 08:30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-07-08 下午</t>
+          <t>2025-08-08 17:30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>左脚受伤</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPM5m8S6_P_r3ND8DNC9CwM04vFLw8JZkISmj1yF4VAA_3024_4032.jpg</t>
+          <t/>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>202507071235000542811</t>
+          <t>202508120852000367370</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2025-07-07 12:35:54</t>
+          <t>2025-08-12 08:52:36</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>朱强</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L51"/>
@@ -5254,35 +5243,36 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2025-07-08 09:42:45</t>
+          <t>2025-08-12 14:59:14</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>朱强提交的请假</t>
+          <t>陈雄提交的请假</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>董磊,钟洪伟</t>
+          <t>段少波,张成林,李锋</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>21:6:51</t>
+          <t>6:6:39</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>朱强|提交申请|2025-07-07 12:35:54|提交申请;
-钟洪伟|审批人|2025-07-07 13:05:13|同意|;
-董磊|直接主管|2025-07-08 09:42:45|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-08 09:42:45|抄送</t>
+          <t>陈雄|提交申请|2025-08-12 08:52:36|提交申请;
+段少波|审批人|2025-08-12 08:58:20|同意|同意|;
+张成林|直接主管|2025-08-12 14:22:49|同意|;
+李锋|直接主管|2025-08-12 14:59:14|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-12 14:59:14|抄送</t>
         </is>
       </c>
     </row>
@@ -5294,32 +5284,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IAdWM9sKR02lpsR4OFaIeQ06491751862856</t>
+          <t>r3fMz1jQTwK3znOQ8IvQhA06491754955661</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-07-07 上午</t>
+          <t>2025-08-13 08:30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-07-08 下午</t>
+          <t>2025-08-13 17:30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>左脚受伤</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5329,59 +5319,61 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>202507071234000162437</t>
+          <t>202508120741000015560</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2025-07-07 12:34:16</t>
+          <t>2025-08-12 07:41:01</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>朱强</t>
+          <t>李庭越</t>
         </is>
       </c>
       <c r="L52"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2025-07-07 12:34:16</t>
+          <t>2025-08-12 11:01:45</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>朱强提交的请假</t>
+          <t>李庭越提交的请假</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t/>
+          <t>张健宁,杜鸣</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0:0:17</t>
+          <t>3:20:45</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>朱强|提交申请|2025-07-07 12:34:16|提交申请;
-朱强|2025-07-07 12:34:33|终止流程实例</t>
+          <t>李庭越|提交申请|2025-08-12 07:41:01|提交申请;
+张健宁|审批人|2025-08-12 08:30:13|同意|;
+杜鸣|直接主管|2025-08-12 11:01:45|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-12 11:01:45|抄送</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5385,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>oIqpUC5MQNGa86RjU-db8w06491751859808</t>
+          <t>48diLsICSmiaggRVfQydWw06491754915938</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5403,12 +5395,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-07-08 08:30</t>
+          <t>2025-08-12 08:30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-07-08 17:30</t>
+          <t>2025-08-12 17:30</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5418,7 +5410,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>家中有事，调休一天，望领导们批准</t>
+          <t xml:space="preserve">调休 </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5428,59 +5420,62 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>202507071143000283539</t>
+          <t>202508112038000583659</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2025-07-07 11:43:28</t>
+          <t>2025-08-11 20:38:58</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>李庭越</t>
+          <t>玉玲珑（魏玉玲）</t>
         </is>
       </c>
       <c r="L53"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2025-07-07 11:43:28</t>
+          <t>2025-08-12 14:59:31</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>李庭越提交的请假</t>
+          <t>玉玲珑（魏玉玲）提交的请假</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t/>
+          <t>李锋,张成林</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>2:40:40</t>
+          <t>18:20:33</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>李庭越|提交申请|2025-07-07 11:43:28|提交申请;
-李庭越|2025-07-07 14:24:07|终止流程实例</t>
+          <t>玉玲珑（魏玉玲）|提交申请|2025-08-11 20:38:58|提交申请;
+李锋|审批人|2025-08-11 22:01:50|同意|同意|;
+张成林|直接主管|2025-08-12 14:22:45|同意|;
+李锋|直接主管|2025-08-12 14:59:31|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-12 14:59:31|抄送</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5487,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A9KtvjXWQeO2KB5HRHH0vQ06491751859568</t>
+          <t>1YWiiglUSWyXIZ7zfHFTqQ06491754903776</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5502,17 +5497,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-07-09 08:30</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-07-09 17:30</t>
+          <t>2025-08-11 13:00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>4小时</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5527,17 +5522,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>202507071139000283106</t>
+          <t>202508111716000166081</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2025-07-07 11:39:28</t>
+          <t>2025-08-11 17:16:16</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>王兴磊</t>
+          <t>祝叶康</t>
         </is>
       </c>
       <c r="L54"/>
@@ -5553,35 +5548,35 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2025-07-09 08:34:45</t>
+          <t>2025-08-11 17:22:13</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>工艺技术部</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>王兴磊提交的请假</t>
+          <t>祝叶康提交的请假</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>张健宁,杜鸣</t>
+          <t>董磊</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>44:55:17</t>
+          <t>0:5:58</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>王兴磊|提交申请|2025-07-07 11:39:28|提交申请;
-张健宁|审批人|2025-07-09 08:32:50|同意|;
-杜鸣|直接主管|2025-07-09 08:34:45|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-09 08:34:46|抄送</t>
+          <t>祝叶康|提交申请|2025-08-11 17:16:16|提交申请;
+董磊|审批人|2025-08-11 17:22:07|同意|;
+董磊|直接主管|2025-08-11 17:22:13|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-11 17:22:13|抄送</t>
         </is>
       </c>
     </row>
@@ -5593,94 +5588,96 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JyEphyQgSa2qQXqG5-3mjQ06491751854565</t>
+          <t>mK9fKJd_TeWTlI-IccWRnw06491754903479</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-07-07 上午</t>
+          <t>2025-08-07 08:30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-07-09 下午</t>
+          <t>2025-08-07 17:30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>高烧，肺炎</t>
+          <t>身体不适</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPD3JsLWYOCm3NBiTNBJywiKaNZceBREAISkkEoK-WAA_1180_1572.jpg</t>
+          <t/>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>202507071016000054705</t>
+          <t>202508111711000196971</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2025-07-07 10:16:05</t>
+          <t>2025-08-11 17:11:19</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>祝叶康</t>
         </is>
       </c>
       <c r="L55"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>审批通过</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>终止</t>
+          <t>已结束</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2025-07-07 10:16:05</t>
+          <t>2025-08-11 17:11:47</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>工艺技术部</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>祝叶康提交的请假</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t/>
+          <t>董磊</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>9:50:37</t>
+          <t>0:0:27</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-07 10:16:05|提交申请;
-王佳忠|2025-07-07 20:06:42|终止流程实例</t>
+          <t>祝叶康|提交申请|2025-08-11 17:11:19|提交申请;
+董磊|审批人|2025-08-11 17:11:39|同意|;
+董磊|直接主管|2025-08-11 17:11:47|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-11 17:11:47|抄送</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5689,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>h-ruXq4tSIiKOw0tHPV54A06491751587956</t>
+          <t>LvBPbmC3Q26MH82Ct25PlQ06491754894516</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5702,58 +5699,58 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-07-04 上午</t>
+          <t>2025-08-11 上午</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-07-04 下午</t>
+          <t>2025-08-17 下午</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>5天</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>下楼梯把脚扭了，开不了车，去趟医院！</t>
+          <t>臀部长了炎性包块，坐立不安</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t/>
+          <t>https://static.dingtalk.com/media/lQDPD4Nvv3B6DJnNELzNFlCwmPKmGVrlUDgId5U7hL0aAA_5712_4284.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>202507040812000368452</t>
+          <t>202508111441000565645</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2025-07-04 08:12:36</t>
+          <t>2025-08-11 14:41:56</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>朱强</t>
+          <t>殷顺威</t>
         </is>
       </c>
       <c r="L56"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2025-07-08 09:42:59</t>
+          <t>2025-08-11 14:41:56</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5763,25 +5760,23 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>朱强提交的请假</t>
+          <t>殷顺威提交的请假</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>董磊,钟洪伟</t>
+          <t/>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>97:30:23</t>
+          <t>27:6:12</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>朱强|提交申请|2025-07-04 08:12:36|提交申请;
-钟洪伟|审批人|2025-07-04 11:01:34|同意|;
-董磊|直接主管|2025-07-08 09:42:59|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-08 09:42:59|抄送</t>
+          <t>殷顺威|提交申请|2025-08-11 14:41:56|提交申请;
+殷顺威|2025-08-12 17:48:07|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5788,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DNG83LZ8Ri-eJdgSMG8UgQ06491751540007</t>
+          <t>axdfHcEARZKZjBxiEOAAJA06491754893393</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5803,22 +5798,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-07-04 下午</t>
+          <t>2025-08-15 上午</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2025-07-10 下午</t>
+          <t>2025-08-15 下午</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4.5天</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>回老家有事</t>
+          <t>家里有事</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5828,17 +5823,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>202507031853000270591</t>
+          <t>202508111423000130482</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2025-07-03 18:53:27</t>
+          <t>2025-08-11 14:23:13</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>梁校</t>
+          <t>葛婷</t>
         </is>
       </c>
       <c r="L57"/>
@@ -5854,36 +5849,35 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2025-07-08 16:15:25</t>
+          <t>2025-08-15 08:33:14</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>营销管理部</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>梁校提交的请假</t>
+          <t>葛婷提交的请假</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>董磊,钟洪伟,李萍</t>
+          <t>周哲敏</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>117:21:58</t>
+          <t>90:10:2</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>梁校|提交申请|2025-07-03 18:53:27|提交申请;
-钟洪伟|审批人|2025-07-04 11:01:27|同意|;
-董磊|直接主管|2025-07-08 09:43:08|同意|;
-李萍|审批人|2025-07-08 16:15:25|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-08 16:15:25|抄送</t>
+          <t>葛婷|提交申请|2025-08-11 14:23:13|提交申请;
+周哲敏|审批人|2025-08-13 19:19:07|同意|;
+周哲敏|直接主管|2025-08-15 08:33:14|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-15 08:33:14|抄送</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5889,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>lLYeqlQnRJWOZISabcxfBw06491751533910</t>
+          <t>cwmkqxW1RCmsswiT1L8v1Q06491754879797</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5905,12 +5899,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-07-04 08:30</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2025-07-04 17:30</t>
+          <t>2025-08-11 17:30</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5920,7 +5914,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>加班抵调休</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5930,17 +5924,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>202507031711000501380</t>
+          <t>202508111036000375844</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2025-07-03 17:11:50</t>
+          <t>2025-08-11 10:36:37</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>沈琪海</t>
+          <t>李庭越</t>
         </is>
       </c>
       <c r="L58"/>
@@ -5956,7 +5950,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2025-07-11 09:12:53</t>
+          <t>2025-08-12 11:01:18</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5966,7 +5960,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>沈琪海提交的请假</t>
+          <t>李庭越提交的请假</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5976,15 +5970,15 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>184:1:4</t>
+          <t>24:24:41</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>沈琪海|提交申请|2025-07-03 17:11:50|提交申请;
-张健宁|审批人|2025-07-11 08:48:51|同意|;
-杜鸣|直接主管|2025-07-11 09:12:54|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-11 09:12:54|抄送</t>
+          <t>李庭越|提交申请|2025-08-11 10:36:37|提交申请;
+张健宁|审批人|2025-08-12 08:30:26|同意|;
+杜鸣|直接主管|2025-08-12 11:01:18|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-12 11:01:18|抄送</t>
         </is>
       </c>
     </row>
@@ -5996,52 +5990,52 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DV7C1-qZQe-PQbN0SwiIHw06491751531394</t>
+          <t>extECW0_QcirAZhLRifWhA06491754876919</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-07-04 上午</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2025-07-04 下午</t>
+          <t>2025-08-11 17:30</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1天</t>
+          <t>8小时</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>持续发烧</t>
+          <t>车间休息，调休一天</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPM5lQEN-oyzXNB4DNBDiwnpnHIXS2JfAIRXg1vDkiAA_1080_1920.jpg</t>
+          <t/>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>202507031629000540716</t>
+          <t>202508110948000393476</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2025-07-03 16:29:54</t>
+          <t>2025-08-11 09:48:39</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>魏军</t>
         </is>
       </c>
       <c r="L59"/>
@@ -6057,35 +6051,36 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2025-07-03 20:08:33</t>
+          <t>2025-08-11 13:48:55</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>魏军提交的请假</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>李锋,张成林</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>3:38:40</t>
+          <t>4:0:16</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-03 16:29:54|提交申请;
-程志鹏|审批人|2025-07-03 19:39:28|同意|尽早去医院就诊|;
-张成林|审批人|2025-07-03 20:08:33|同意|阳了嘛？|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-03 20:08:34|抄送</t>
+          <t>魏军|提交申请|2025-08-11 09:48:39|提交申请;
+李锋|审批人|2025-08-11 09:54:12|同意|同意|;
+张成林|直接主管|2025-08-11 12:55:48|同意|;
+李锋|直接主管|2025-08-11 13:48:55|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-11 13:48:55|抄送</t>
         </is>
       </c>
     </row>
@@ -6097,32 +6092,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2IpsT8IWThGbLiUBWy9o2A06491751502000</t>
+          <t>e2bsNuI1RHKZlEHeuWWlvg06491754874402</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-07-04 08:30</t>
+          <t>2025-08-11 上午</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2025-07-04 17:30</t>
+          <t>2025-08-11 上午</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>8小时</t>
+          <t>0.5天</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>周末有生产任务调休一天</t>
+          <t>小孩肺炎出院，需要请假2小时接送，提前办手续</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6132,17 +6127,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>202507030820000006245</t>
+          <t>202508110906000426909</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2025-07-03 08:20:00</t>
+          <t>2025-08-11 09:06:42</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>李庭越</t>
+          <t>郑翔</t>
         </is>
       </c>
       <c r="L60"/>
@@ -6158,35 +6153,35 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2025-07-11 09:12:42</t>
+          <t>2025-08-11 10:14:35</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>仓储物流部</t>
+          <t>信息与品宣部</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>李庭越提交的请假</t>
+          <t>郑翔提交的请假</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>张健宁,杜鸣</t>
+          <t>杜以烽</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>192:52:43</t>
+          <t>1:7:53</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>李庭越|提交申请|2025-07-03 08:20:00|提交申请;
-张健宁|审批人|2025-07-11 08:49:01|同意|;
-杜鸣|直接主管|2025-07-11 09:12:42|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-11 09:12:42|抄送</t>
+          <t>郑翔|提交申请|2025-08-11 09:06:42|提交申请;
+杜以烽|审批人|2025-08-11 10:14:17|同意|;
+杜以烽|直接主管|2025-08-11 10:14:35|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-11 10:14:35|抄送</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6193,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>-Xz5MsveRHyKdu0MAw8Q-Q06491751463258</t>
+          <t>gbcpBj9lTVeXmX1jihsQgg06491754870795</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6208,12 +6203,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-07-03 08:30</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2025-07-03 17:30</t>
+          <t>2025-08-11 17:30</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6223,7 +6218,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>调休一天，望批准</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6233,62 +6228,59 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>202507022134000188961</t>
+          <t>202508110806000353958</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2025-07-02 21:34:18</t>
+          <t>2025-08-11 08:06:35</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>董凯宁</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L61"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2025-07-03 19:02:59</t>
+          <t>2025-08-11 08:06:35</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>董凯宁提交的请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t/>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>21:28:41</t>
+          <t>0:3:56</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>董凯宁|提交申请|2025-07-02 21:34:18|提交申请;
-李锋|审批人|2025-07-03 07:35:27|同意|同意|;
-张成林|直接主管|2025-07-03 15:09:37|同意|;
-李锋|直接主管|2025-07-03 19:02:59|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-03 19:02:59|抄送</t>
+          <t>王兴磊|提交申请|2025-08-11 08:06:35|提交申请;
+王兴磊|2025-08-11 08:10:31|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6292,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wc2pip6fQE6bRwzW4DhwcQ06491751442114</t>
+          <t>dK6Ujpj1QHGDkCcMvs0ZeQ06491754815860</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6310,12 +6302,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-07-04 08:30</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2025-07-04 18:00</t>
+          <t>2025-08-11 17:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6325,7 +6317,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>调休处理个人事务</t>
+          <t>调休一天</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6335,62 +6327,59 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>202507021541000545371</t>
+          <t>202508101651000005578</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2025-07-02 15:41:54</t>
+          <t>2025-08-10 16:51:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>李奇</t>
+          <t>王兴磊</t>
         </is>
       </c>
       <c r="L62"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>审批通过</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>已结束</t>
+          <t>终止</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2025-07-03 07:35:05</t>
+          <t>2025-08-10 16:51:00</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>质量保证部</t>
+          <t>仓储物流部</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>李奇提交的请假</t>
+          <t>王兴磊提交的请假</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>李锋,张成林</t>
+          <t/>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>15:53:12</t>
+          <t>6:1:37</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>李奇|提交申请|2025-07-02 15:41:54|提交申请;
-李锋|审批人|2025-07-02 19:44:46|同意|同意|;
-张成林|直接主管|2025-07-02 21:59:28|同意|;
-李锋|直接主管|2025-07-03 07:35:05|同意|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-03 07:35:05|抄送</t>
+          <t>王兴磊|提交申请|2025-08-10 16:51:00|提交申请;
+王兴磊|2025-08-10 22:52:38|终止流程实例</t>
         </is>
       </c>
     </row>
@@ -6402,52 +6391,52 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nHvr_RxbTjOl6SGp6tSkvQ06491751436125</t>
+          <t>WrCSurR9SpipP9Tz8tBhcQ06491754693218</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>病假</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-07-02 下午</t>
+          <t>2025-08-11 08:30</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2025-07-03 下午</t>
+          <t>2025-08-12 18:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1.5天</t>
+          <t>16小时</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>发烧，腰痛</t>
+          <t>加班转调休</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://static.dingtalk.com/media/lQDPM4JuApe_323ND8DNC9Cw9-KG3-mm6a4IRAzW6iClAA_3024_4032.jpg</t>
+          <t/>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>202507021402000058223</t>
+          <t>202508090646000585027</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-07-02 14:02:05</t>
+          <t>2025-08-09 06:46:58</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>王佳忠</t>
+          <t>胡俊杨</t>
         </is>
       </c>
       <c r="L63"/>
@@ -6463,35 +6452,35 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2025-07-03 00:22:37</t>
+          <t>2025-08-09 08:29:13</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t/>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>王佳忠提交的请假</t>
+          <t>胡俊杨提交的请假</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>董磊</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>10:20:32</t>
+          <t>1:42:16</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>王佳忠|提交申请|2025-07-02 14:02:05|提交申请;
-程志鹏|审批人|2025-07-02 14:49:52|同意|;
-张成林|审批人|2025-07-03 00:22:37|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-03 00:22:37|抄送</t>
+          <t>胡俊杨(已离职)|提交申请|2025-08-09 06:46:58|提交申请;
+董磊|审批人|2025-08-09 08:22:17|同意|;
+董磊|直接主管|2025-08-09 08:29:13|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-09 08:29:14|抄送</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6492,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>oh6sEGF3SkClsXNKz-8bMw06491751355887</t>
+          <t>S6sGJsPFQT-KkMMceWK0Ew06491754656461</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6513,12 +6502,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-06-11 08:30</t>
+          <t>2025-08-09 08:30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2025-06-11 17:30</t>
+          <t>2025-08-09 17:30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6528,7 +6517,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>调休一天，望批准</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6538,17 +6527,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>202507011544000476020</t>
+          <t>202508082034000223180</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2025-07-01 15:44:47</t>
+          <t>2025-08-08 20:34:22</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>秦国超</t>
+          <t>董凯宁</t>
         </is>
       </c>
       <c r="L64"/>
@@ -6564,35 +6553,36 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2025-07-03 13:47:17</t>
+          <t>2025-08-10 08:10:25</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>生产管理部</t>
+          <t>质量保证部</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>秦国超提交的请假</t>
+          <t>董凯宁提交的请假</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>钟洪伟,董磊</t>
+          <t>张成林,李锋</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>46:2:29</t>
+          <t>35:36:4</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>秦国超|提交申请|2025-07-01 15:44:47|提交申请;
-钟洪伟|审批人|2025-07-03 12:36:40|同意|;
-董磊|直接主管|2025-07-03 13:47:17|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-03 13:47:17|抄送</t>
+          <t>董凯宁|提交申请|2025-08-08 20:34:22|提交申请;
+李锋|审批人|2025-08-09 08:23:41|同意|同意|;
+张成林|直接主管|2025-08-09 23:52:17|同意|;
+李锋|直接主管|2025-08-10 08:10:25|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-10 08:10:25|抄送</t>
         </is>
       </c>
     </row>
@@ -6604,33 +6594,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0AHDGo_AQUKfMnRu5IS3fA06491751339704</t>
+          <t>PlBrrP03T5SSK-4lBUmv0A06491754615249</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-07-01 11:30</t>
+          <t>2025-07-28 上午</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2025-07-01 18:00</t>
+          <t>2025-07-28 下午</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>5小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>因头晕头痛身体不适调休半天休息；
-用6月5日和6月12日累计加班5.5h换！</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6640,17 +6629,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>202507011115000046324</t>
+          <t>202508080907000296425</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2025-07-01 11:15:04</t>
+          <t>2025-08-08 09:07:29</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>高剑濠</t>
+          <t>张曙光</t>
         </is>
       </c>
       <c r="L65"/>
@@ -6666,35 +6655,36 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2025-07-01 13:48:29</t>
+          <t>2025-08-08 15:02:09</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t/>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>高剑濠提交的请假</t>
+          <t>张曙光提交的请假</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>张成林,程志鹏</t>
+          <t>张成林,李锋</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>2:33:26</t>
+          <t>5:54:40</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>高剑濠|提交申请|2025-07-01 11:15:04|提交申请;
-程志鹏|审批人|2025-07-01 12:01:35|同意|;
-张成林|审批人|2025-07-01 13:48:30|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-01 13:48:30|抄送</t>
+          <t>张曙光(已离职)|提交申请|2025-08-08 09:07:29|提交申请;
+李锋|审批人|2025-08-08 10:00:43|同意|同意|;
+张成林|直接主管|2025-08-08 14:18:34|同意|;
+李锋|直接主管|2025-08-08 15:02:09|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-08 15:02:10|抄送</t>
         </is>
       </c>
     </row>
@@ -6706,32 +6696,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KKzpwxpeQaKLhuN3AOm1CA06491751332358</t>
+          <t>F6Cica_dQbKjaOVlKAhuvQ06491754615206</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>调休</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-07-10 08:30</t>
+          <t>2025-07-14 上午</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2025-07-10 10:30</t>
+          <t>2025-07-14 下午</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2小时</t>
+          <t>1天</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>办理业务</t>
+          <t>事假</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6741,17 +6731,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>202507010912000388095</t>
+          <t>202508080906000468838</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2025-07-01 09:12:38</t>
+          <t>2025-08-08 09:06:46</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>韦东略</t>
+          <t>张曙光</t>
         </is>
       </c>
       <c r="L66"/>
@@ -6767,35 +6757,36 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2025-07-01 11:30:45</t>
+          <t>2025-08-08 15:01:59</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>试验科</t>
+          <t/>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>韦东略提交的请假</t>
+          <t>张曙光提交的请假</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>程志鹏,张成林</t>
+          <t>李锋,张成林</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>2:18:7</t>
+          <t>5:55:13</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>韦东略|提交申请|2025-07-01 09:12:38|提交申请;
-程志鹏|审批人|2025-07-01 09:16:00|同意|;
-张成林|审批人|2025-07-01 11:30:45|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-01 11:30:45|抄送</t>
+          <t>张曙光(已离职)|提交申请|2025-08-08 09:06:46|提交申请;
+李锋|审批人|2025-08-08 10:00:58|同意|同意|;
+张成林|直接主管|2025-08-08 14:18:41|同意|;
+李锋|直接主管|2025-08-08 15:01:59|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-08 15:02:00|抄送</t>
         </is>
       </c>
     </row>
@@ -6807,7 +6798,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>i24t0ZxNQBqjFDb5FTHXBw06491751306459</t>
+          <t>sVtJjvGiQJWD-Mob3rGJAw06491754546941</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6817,12 +6808,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-01 08:30</t>
+          <t>2025-07-19 08:30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2025-07-01 18:00</t>
+          <t>2025-07-19 17:30</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6832,7 +6823,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>外耳道炎复诊</t>
+          <t>调休</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6842,17 +6833,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>202507010200000597877</t>
+          <t>202508071409000015095</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2025-07-01 02:00:59</t>
+          <t>2025-08-07 14:09:01</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>陈雄</t>
         </is>
       </c>
       <c r="L67"/>
@@ -6868,35 +6859,845 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2025-07-01 09:56:11</t>
+          <t>2025-08-07 19:55:44</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
+          <t>质量保证部</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>陈雄提交的请假</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>段少波,董磊</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>5:46:44</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>陈雄|提交申请|2025-08-07 14:09:01|提交申请;
+段少波|审批人|2025-08-07 19:48:17|同意|同意|;
+董磊|直接主管|2025-08-07 19:55:44|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-07 19:55:44|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>JPq7ZapWTb2dEGgvLDMfsQ06491754526376</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-08-07 08:30</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-08-07 09:30</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1小时</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>修车</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>202508070826000162157</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2025-08-07 08:26:16</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>朱强</t>
+        </is>
+      </c>
+      <c r="L68"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2025-08-07 13:43:00</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
           <t>生产管理部</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>李俊杰提交的请假</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>朱强提交的请假</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>钟洪伟,董磊</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>7:55:12</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>李俊杰|提交申请|2025-07-01 02:00:59|提交申请;
-钟洪伟|审批人|2025-07-01 09:55:50|同意|;
-董磊|直接主管|2025-07-01 09:56:11|同意|;
-曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-07-01 09:56:11|抄送</t>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>5:16:43</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>朱强|提交申请|2025-08-07 08:26:16|提交申请;
+钟洪伟|审批人|2025-08-07 13:07:03|同意|;
+董磊|直接主管|2025-08-07 13:43:00|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-07 13:43:00|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>6VshhwirSU-SVYOa9bedrA06491754476519</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-08-09 08:30</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-08-09 17:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>8小时</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>调休一天</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>202508061835000198032</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2025-08-06 18:35:19</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>王兴磊</t>
+        </is>
+      </c>
+      <c r="L69"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2025-08-07 19:10:50</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>仓储物流部</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>王兴磊提交的请假</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>张健宁,杜鸣</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>24:35:32</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>王兴磊|提交申请|2025-08-06 18:35:19|提交申请;
+张健宁|审批人|2025-08-06 21:36:07|同意|;
+杜鸣|直接主管|2025-08-07 19:10:50|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-07 19:10:50|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3R-GE0C6TWiHuIyo2BnGQQ06491754473070</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-08-07 08:30</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-08-07 17:30</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>8小时</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>202508061737000504968</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2025-08-06 17:37:50</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>玉玲珑（魏玉玲）</t>
+        </is>
+      </c>
+      <c r="L70"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2025-08-06 19:43:14</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>质量保证部</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>玉玲珑（魏玉玲）提交的请假</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>张成林,李锋</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>2:5:24</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>玉玲珑（魏玉玲）|提交申请|2025-08-06 17:37:50|提交申请;
+李锋|审批人|2025-08-06 18:18:07|同意|同意|;
+张成林|直接主管|2025-08-06 19:11:37|同意|;
+李锋|直接主管|2025-08-06 19:43:14|同意|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-06 19:43:14|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NBMwPu1FQEC4gbuv_UFBDw06491754300026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-08-05 08:30</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-08-05 17:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>8小时</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>调休一天</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>202508041733000460353</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2025-08-04 17:33:46</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>李庭越</t>
+        </is>
+      </c>
+      <c r="L71"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2025-08-06 09:09:38</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>仓储物流部</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>李庭越提交的请假</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>杜鸣,张健宁</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>39:35:52</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>李庭越|提交申请|2025-08-04 17:33:46|提交申请;
+张健宁|审批人|2025-08-05 09:25:54|同意|;
+杜鸣|直接主管|2025-08-06 09:09:38|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-06 09:09:38|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>aByfCRGPQUy_LMkgAQf3GQ06491754228002</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-08-04 08:30</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-08-04 18:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>8小时</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>202508032133000222635</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2025-08-03 21:33:22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>韦东略</t>
+        </is>
+      </c>
+      <c r="L72"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2025-08-04 08:40:21</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>试验科</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>韦东略提交的请假</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>张成林,程志鹏</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>11:6:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>韦东略|提交申请|2025-08-03 21:33:22|提交申请;
+程志鹏|审批人|2025-08-03 23:29:41|同意|;
+张成林|审批人|2025-08-04 08:40:21|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-04 08:40:21|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>aeELKBe-SEmMfRK6iK6ITQ06491754126575</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-08-04 08:30</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-08-05 18:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>16小时</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>由于外婆不幸去世，要给外婆守夜和送外婆</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>202508021722000554216</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2025-08-02 17:22:55</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>夏天龙</t>
+        </is>
+      </c>
+      <c r="L73"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2025-08-04 08:40:46</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>试验科</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>夏天龙提交的请假</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>张成林,程志鹏</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>39:17:52</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>夏天龙|提交申请|2025-08-02 17:22:55|提交申请;
+程志鹏|审批人|2025-08-03 10:25:40|同意|;
+张成林|审批人|2025-08-04 08:40:46|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-04 08:40:46|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3GwxN2MzTwyVtbgQtR-lNw06491754044693</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>调休</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-08-02 08:30</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-08-02 17:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>8小时</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调休一天
+</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>202508011838000132416</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2025-08-01 18:38:13</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>王兴磊</t>
+        </is>
+      </c>
+      <c r="L74"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2025-08-03 09:53:29</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>仓储物流部</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>王兴磊提交的请假</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>杜鸣,张健宁</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>39:15:16</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>王兴磊|提交申请|2025-08-01 18:38:13|提交申请;
+张健宁|审批人|2025-08-01 20:40:38|同意|;
+杜鸣|直接主管|2025-08-03 09:53:29|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-03 09:53:29|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>rXg0kz9CTQWdvWYf8fONSQ06491754022736</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>事假</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-08-01 下午</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-08-01 下午</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.5天</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>家里有事</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>202508011232000165065</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2025-08-01 12:32:17</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>朱强</t>
+        </is>
+      </c>
+      <c r="L75"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2025-08-04 08:15:17</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>生产管理部</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>朱强提交的请假</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>钟洪伟,董磊</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>67:43:1</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>朱强|提交申请|2025-08-01 12:32:16|提交申请;
+钟洪伟|审批人|2025-08-04 07:04:08|同意|;
+董磊|直接主管|2025-08-04 08:15:17|同意|;
+曾婷婷,尹娜,周哲敏,李萍|抄送人|2025-08-04 08:15:17|抄送</t>
         </is>
       </c>
     </row>
